--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2468,7 +2468,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3101,7 +3101,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3826,7 +3826,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -4553,7 +4553,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -5259,7 +5259,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -5992,7 +5992,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -6707,7 +6707,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -7446,7 +7446,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -8197,7 +8197,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -8924,7 +8924,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -9670,7 +9670,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10351,7 +10351,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10610,16 +10610,20 @@
         <f t="shared" si="1"/>
         <v>46276</v>
       </c>
-      <c r="D14" s="4"/>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="1"/>
+      <c r="G14" s="1">
+        <v>12</v>
+      </c>
       <c r="H14" s="1">
         <v>20</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="15" spans="2:21" x14ac:dyDescent="0.3">
@@ -10627,16 +10631,20 @@
         <f t="shared" si="1"/>
         <v>46277</v>
       </c>
-      <c r="D15" s="4"/>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1">
+        <v>10</v>
+      </c>
       <c r="H15" s="1">
         <v>20</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16" spans="2:21" x14ac:dyDescent="0.3">
@@ -10644,16 +10652,20 @@
         <f t="shared" si="1"/>
         <v>46278</v>
       </c>
-      <c r="D16" s="4"/>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
-      <c r="G16" s="1"/>
+      <c r="G16" s="1">
+        <v>12</v>
+      </c>
       <c r="H16" s="1">
         <v>20</v>
       </c>
       <c r="I16" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="17" spans="3:9" x14ac:dyDescent="0.3">
@@ -10948,21 +10960,21 @@
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E35" s="5">
         <f>D35/30</f>
-        <v>0.1</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>11.8</v>
+        <v>11.692307692307692</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.19666666666666668</v>
+        <v>0.2533333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -11698,7 +11710,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -12631,7 +12643,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -13744,7 +13756,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -14459,7 +14471,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -15189,7 +15201,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -15895,7 +15907,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -16622,7 +16634,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2468,7 +2468,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3101,7 +3101,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3826,7 +3826,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -4553,7 +4553,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -5259,7 +5259,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -5992,7 +5992,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -6707,7 +6707,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -7446,7 +7446,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -8197,7 +8197,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -8924,7 +8924,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -9670,7 +9670,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10351,7 +10351,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10673,16 +10673,20 @@
         <f t="shared" si="1"/>
         <v>46279</v>
       </c>
-      <c r="D17" s="4"/>
+      <c r="D17" s="4">
+        <v>0</v>
+      </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
-      <c r="G17" s="1"/>
+      <c r="G17" s="1">
+        <v>13</v>
+      </c>
       <c r="H17" s="1">
         <v>20</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="18" spans="3:9" x14ac:dyDescent="0.3">
@@ -10969,12 +10973,12 @@
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>11.692307692307692</v>
+        <v>11.785714285714286</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.2533333333333333</v>
+        <v>0.27500000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -11710,7 +11714,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -12643,7 +12647,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -13756,7 +13760,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -14471,7 +14475,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -15201,7 +15205,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -15907,7 +15911,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -16634,7 +16638,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -54,6 +54,147 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>서진철</author>
+  </authors>
+  <commentList>
+    <comment ref="G18" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>서진철</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>진짜</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>문제긴</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>하지</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">? </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>ㅋ
+정신</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>차립시다</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>!</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>서진철</author>
@@ -258,7 +399,7 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>서진철</author>
@@ -1123,7 +1264,7 @@
 </comments>
 </file>
 
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>tc={1FE270D1-E093-46D6-8986-1715CA56D0D3}</author>
@@ -2468,7 +2609,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3101,7 +3242,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3826,7 +3967,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -4553,7 +4694,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -5259,7 +5400,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -5992,7 +6133,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -6707,7 +6848,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -7446,7 +7587,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -8197,7 +8338,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -8924,7 +9065,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -9670,7 +9811,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10330,7 +10471,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:U35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10351,7 +10492,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10694,16 +10835,20 @@
         <f t="shared" si="1"/>
         <v>46280</v>
       </c>
-      <c r="D18" s="4"/>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
-      <c r="G18" s="1"/>
+      <c r="G18" s="1">
+        <v>15</v>
+      </c>
       <c r="H18" s="1">
         <v>20</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="19" spans="3:9" x14ac:dyDescent="0.3">
@@ -10964,21 +11109,21 @@
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E35" s="5">
         <f>D35/30</f>
-        <v>0.16666666666666666</v>
+        <v>0.2</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>11.785714285714286</v>
+        <v>12</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.27500000000000002</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -11004,6 +11149,7 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -11714,7 +11860,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -12647,7 +12793,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -13760,7 +13906,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -14475,7 +14621,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -15205,7 +15351,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -15911,7 +16057,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -16638,7 +16784,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2609,7 +2609,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3242,7 +3242,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3967,7 +3967,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -4694,7 +4694,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -5400,7 +5400,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -6133,7 +6133,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -6848,7 +6848,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -7587,7 +7587,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -8338,7 +8338,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -9065,7 +9065,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -9811,7 +9811,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10492,7 +10492,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10856,16 +10856,20 @@
         <f t="shared" si="1"/>
         <v>46281</v>
       </c>
-      <c r="D19" s="4"/>
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
-      <c r="G19" s="1"/>
+      <c r="G19" s="1">
+        <v>12</v>
+      </c>
       <c r="H19" s="1">
         <v>20</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="20" spans="3:9" x14ac:dyDescent="0.3">
@@ -11109,11 +11113,11 @@
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E35" s="5">
         <f>D35/30</f>
-        <v>0.2</v>
+        <v>0.23333333333333334</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
@@ -11123,7 +11127,7 @@
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -11860,7 +11864,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -12793,7 +12797,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -13906,7 +13910,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -14621,7 +14625,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -15351,7 +15355,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -16057,7 +16061,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -16784,7 +16788,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2609,7 +2609,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3242,7 +3242,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3967,7 +3967,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -4694,7 +4694,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -5400,7 +5400,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -6133,7 +6133,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -6848,7 +6848,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -7587,7 +7587,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -8338,7 +8338,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -9065,7 +9065,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -9811,7 +9811,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10492,7 +10492,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10877,16 +10877,20 @@
         <f t="shared" si="1"/>
         <v>46282</v>
       </c>
-      <c r="D20" s="4"/>
+      <c r="D20" s="4">
+        <v>0</v>
+      </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
-      <c r="G20" s="1"/>
+      <c r="G20" s="1">
+        <v>13</v>
+      </c>
       <c r="H20" s="1">
         <v>20</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="21" spans="3:9" x14ac:dyDescent="0.3">
@@ -11122,12 +11126,12 @@
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>12</v>
+        <v>12.058823529411764</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.32</v>
+        <v>0.34166666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -11864,7 +11868,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -12797,7 +12801,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -13910,7 +13914,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -14625,7 +14629,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -15355,7 +15359,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -16061,7 +16065,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -16788,7 +16792,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2609,7 +2609,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3242,7 +3242,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3967,7 +3967,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -4694,7 +4694,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -5400,7 +5400,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -6133,7 +6133,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -6848,7 +6848,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -7587,7 +7587,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -8338,7 +8338,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -9065,7 +9065,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -9811,7 +9811,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10492,7 +10492,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10898,16 +10898,20 @@
         <f t="shared" si="1"/>
         <v>46283</v>
       </c>
-      <c r="D21" s="4"/>
+      <c r="D21" s="4">
+        <v>1</v>
+      </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
-      <c r="G21" s="1"/>
+      <c r="G21" s="1">
+        <v>13</v>
+      </c>
       <c r="H21" s="1">
         <v>20</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="22" spans="3:9" x14ac:dyDescent="0.3">
@@ -10915,16 +10919,20 @@
         <f t="shared" si="1"/>
         <v>46284</v>
       </c>
-      <c r="D22" s="4"/>
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
-      <c r="G22" s="1"/>
+      <c r="G22" s="1">
+        <v>8</v>
+      </c>
       <c r="H22" s="1">
         <v>20</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="23" spans="3:9" x14ac:dyDescent="0.3">
@@ -10932,16 +10940,20 @@
         <f t="shared" si="1"/>
         <v>46285</v>
       </c>
-      <c r="D23" s="4"/>
+      <c r="D23" s="4">
+        <v>0</v>
+      </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
-      <c r="G23" s="1"/>
+      <c r="G23" s="1">
+        <v>11</v>
+      </c>
       <c r="H23" s="1">
         <v>20</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="24" spans="3:9" x14ac:dyDescent="0.3">
@@ -11117,21 +11129,21 @@
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E35" s="5">
         <f>D35/30</f>
-        <v>0.23333333333333334</v>
+        <v>0.26666666666666666</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>12.058823529411764</v>
+        <v>11.85</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.34166666666666667</v>
+        <v>0.39500000000000007</v>
       </c>
     </row>
   </sheetData>
@@ -11868,7 +11880,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -12801,7 +12813,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -13914,7 +13926,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -14629,7 +14641,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -15359,7 +15371,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -16065,7 +16077,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -16792,7 +16804,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2609,7 +2609,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3242,7 +3242,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3967,7 +3967,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -4694,7 +4694,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -5400,7 +5400,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -6133,7 +6133,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -6848,7 +6848,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -7587,7 +7587,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -8338,7 +8338,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -9065,7 +9065,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -9811,7 +9811,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10492,7 +10492,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10961,16 +10961,20 @@
         <f t="shared" si="1"/>
         <v>46286</v>
       </c>
-      <c r="D24" s="4"/>
+      <c r="D24" s="4">
+        <v>0</v>
+      </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
-      <c r="G24" s="1"/>
+      <c r="G24" s="1">
+        <v>12</v>
+      </c>
       <c r="H24" s="1">
         <v>20</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="25" spans="3:9" x14ac:dyDescent="0.3">
@@ -11138,12 +11142,12 @@
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>11.85</v>
+        <v>11.857142857142858</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.39500000000000007</v>
+        <v>0.41500000000000004</v>
       </c>
     </row>
   </sheetData>
@@ -11880,7 +11884,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -12813,7 +12817,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -13926,7 +13930,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -14641,7 +14645,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -15371,7 +15375,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -16077,7 +16081,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -16804,7 +16808,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2609,7 +2609,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3242,7 +3242,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3967,7 +3967,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -4694,7 +4694,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -5400,7 +5400,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -6133,7 +6133,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -6848,7 +6848,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -7587,7 +7587,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -8338,7 +8338,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -9065,7 +9065,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -9811,7 +9811,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10492,7 +10492,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10982,16 +10982,20 @@
         <f t="shared" si="1"/>
         <v>46287</v>
       </c>
-      <c r="D25" s="4"/>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
-      <c r="G25" s="1"/>
+      <c r="G25" s="1">
+        <v>13</v>
+      </c>
       <c r="H25" s="1">
         <v>20</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="26" spans="3:9" x14ac:dyDescent="0.3">
@@ -11142,12 +11146,12 @@
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>11.857142857142858</v>
+        <v>11.909090909090908</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.41500000000000004</v>
+        <v>0.4366666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -11884,7 +11888,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -12817,7 +12821,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -13930,7 +13934,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -14645,7 +14649,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -15375,7 +15379,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -16081,7 +16085,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -16808,7 +16812,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2609,7 +2609,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3242,7 +3242,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3967,7 +3967,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -4694,7 +4694,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -5400,7 +5400,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -6133,7 +6133,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -6848,7 +6848,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -7587,7 +7587,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -8338,7 +8338,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -9065,7 +9065,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -9811,7 +9811,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10492,7 +10492,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -11003,16 +11003,20 @@
         <f t="shared" si="1"/>
         <v>46288</v>
       </c>
-      <c r="D26" s="4"/>
+      <c r="D26" s="4">
+        <v>0</v>
+      </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
-      <c r="G26" s="1"/>
+      <c r="G26" s="1">
+        <v>13</v>
+      </c>
       <c r="H26" s="1">
         <v>20</v>
       </c>
       <c r="I26" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="27" spans="3:9" x14ac:dyDescent="0.3">
@@ -11020,16 +11024,20 @@
         <f t="shared" si="1"/>
         <v>46289</v>
       </c>
-      <c r="D27" s="4"/>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
-      <c r="G27" s="1"/>
+      <c r="G27" s="1">
+        <v>13</v>
+      </c>
       <c r="H27" s="1">
         <v>20</v>
       </c>
       <c r="I27" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="28" spans="3:9" x14ac:dyDescent="0.3">
@@ -11037,16 +11045,20 @@
         <f t="shared" si="1"/>
         <v>46290</v>
       </c>
-      <c r="D28" s="4"/>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
-      <c r="G28" s="1"/>
+      <c r="G28" s="1">
+        <v>12</v>
+      </c>
       <c r="H28" s="1">
         <v>20</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="29" spans="3:9" x14ac:dyDescent="0.3">
@@ -11054,16 +11066,20 @@
         <f t="shared" si="1"/>
         <v>46291</v>
       </c>
-      <c r="D29" s="4"/>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
-      <c r="G29" s="1"/>
+      <c r="G29" s="1">
+        <v>13</v>
+      </c>
       <c r="H29" s="1">
         <v>20</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="30" spans="3:9" x14ac:dyDescent="0.3">
@@ -11071,16 +11087,20 @@
         <f t="shared" si="1"/>
         <v>46292</v>
       </c>
-      <c r="D30" s="4"/>
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="1"/>
+      <c r="G30" s="1">
+        <v>12</v>
+      </c>
       <c r="H30" s="1">
         <v>20</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="31" spans="3:9" x14ac:dyDescent="0.3">
@@ -11137,21 +11157,21 @@
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E35" s="5">
         <f>D35/30</f>
-        <v>0.26666666666666666</v>
+        <v>0.3</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>11.909090909090908</v>
+        <v>12.037037037037036</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.4366666666666667</v>
+        <v>0.54166666666666674</v>
       </c>
     </row>
   </sheetData>
@@ -11888,7 +11908,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -12821,7 +12841,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -13934,7 +13954,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -14649,7 +14669,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -15379,7 +15399,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -16085,7 +16105,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -16812,7 +16832,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1293,7 +1293,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="38">
   <si>
     <t>매일 운동하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1442,6 +1442,10 @@
     <t>끝나자마자 바로 기록할 필요가 있다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>9 Challenge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1558,7 +1562,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1639,6 +1643,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2588,89 +2595,98 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:U36"/>
+  <dimension ref="B2:W36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="0.875" customWidth="1"/>
-    <col min="19" max="21" width="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="0.75" customWidth="1"/>
+    <col min="7" max="7" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="0.75" customWidth="1"/>
+    <col min="13" max="13" width="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.25" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="0.875" customWidth="1"/>
+    <col min="21" max="23" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="29"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="29" t="s">
-        <v>1</v>
+      <c r="D3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="30"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="K3" s="1" t="s">
+      <c r="I3" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="M3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="R3" s="1"/>
-      <c r="S3" s="1" t="s">
+      <c r="T3" s="1"/>
+      <c r="U3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="V3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="W3" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
         <v>46113</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1">
+        <v>20</v>
+      </c>
+      <c r="K4" s="5">
+        <f>I4/J4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C5" s="3">
         <f>C4+1</f>
         <v>46114</v>
@@ -2678,16 +2694,18 @@
       <c r="D5" s="4"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1">
+        <v>20</v>
+      </c>
+      <c r="K5" s="5">
+        <f t="shared" ref="K5:K34" si="0">I5/J5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C6" s="3">
         <f t="shared" ref="C6:C34" si="1">C5+1</f>
         <v>46115</v>
@@ -2695,16 +2713,18 @@
       <c r="D6" s="4"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1">
+        <v>20</v>
+      </c>
+      <c r="K6" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C7" s="3">
         <f t="shared" si="1"/>
         <v>46116</v>
@@ -2712,16 +2732,18 @@
       <c r="D7" s="4"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1">
+        <v>20</v>
+      </c>
+      <c r="K7" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C8" s="3">
         <f t="shared" si="1"/>
         <v>46117</v>
@@ -2729,16 +2751,18 @@
       <c r="D8" s="4"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1">
+        <v>20</v>
+      </c>
+      <c r="K8" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C9" s="3">
         <f t="shared" si="1"/>
         <v>46118</v>
@@ -2746,16 +2770,18 @@
       <c r="D9" s="4"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1">
+        <v>20</v>
+      </c>
+      <c r="K9" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C10" s="3">
         <f t="shared" si="1"/>
         <v>46119</v>
@@ -2763,16 +2789,18 @@
       <c r="D10" s="4"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1">
+        <v>20</v>
+      </c>
+      <c r="K10" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C11" s="3">
         <f t="shared" si="1"/>
         <v>46120</v>
@@ -2780,16 +2808,18 @@
       <c r="D11" s="4"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1">
+        <v>20</v>
+      </c>
+      <c r="K11" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C12" s="3">
         <f t="shared" si="1"/>
         <v>46121</v>
@@ -2797,16 +2827,18 @@
       <c r="D12" s="4"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1">
+        <v>20</v>
+      </c>
+      <c r="K12" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C13" s="3">
         <f t="shared" si="1"/>
         <v>46122</v>
@@ -2814,16 +2846,18 @@
       <c r="D13" s="4"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1">
+        <v>20</v>
+      </c>
+      <c r="K13" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C14" s="3">
         <f t="shared" si="1"/>
         <v>46123</v>
@@ -2831,16 +2865,18 @@
       <c r="D14" s="4"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1">
+        <v>20</v>
+      </c>
+      <c r="K14" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C15" s="3">
         <f t="shared" si="1"/>
         <v>46124</v>
@@ -2848,16 +2884,18 @@
       <c r="D15" s="4"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1">
+        <v>20</v>
+      </c>
+      <c r="K15" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C16" s="3">
         <f t="shared" si="1"/>
         <v>46125</v>
@@ -2865,16 +2903,18 @@
       <c r="D16" s="4"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1">
+        <v>20</v>
+      </c>
+      <c r="K16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C17" s="3">
         <f t="shared" si="1"/>
         <v>46126</v>
@@ -2882,16 +2922,18 @@
       <c r="D17" s="4"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1">
+        <v>20</v>
+      </c>
+      <c r="K17" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C18" s="3">
         <f t="shared" si="1"/>
         <v>46127</v>
@@ -2899,16 +2941,18 @@
       <c r="D18" s="4"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1">
+        <v>20</v>
+      </c>
+      <c r="K18" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C19" s="3">
         <f t="shared" si="1"/>
         <v>46128</v>
@@ -2916,16 +2960,18 @@
       <c r="D19" s="4"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1">
+        <v>20</v>
+      </c>
+      <c r="K19" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C20" s="3">
         <f t="shared" si="1"/>
         <v>46129</v>
@@ -2933,16 +2979,18 @@
       <c r="D20" s="4"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1">
+        <v>20</v>
+      </c>
+      <c r="K20" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C21" s="3">
         <f t="shared" si="1"/>
         <v>46130</v>
@@ -2950,16 +2998,18 @@
       <c r="D21" s="4"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1">
+        <v>20</v>
+      </c>
+      <c r="K21" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C22" s="3">
         <f t="shared" si="1"/>
         <v>46131</v>
@@ -2967,16 +3017,18 @@
       <c r="D22" s="4"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1">
+        <v>20</v>
+      </c>
+      <c r="K22" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C23" s="3">
         <f t="shared" si="1"/>
         <v>46132</v>
@@ -2984,16 +3036,18 @@
       <c r="D23" s="4"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1">
+        <v>20</v>
+      </c>
+      <c r="K23" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C24" s="3">
         <f t="shared" si="1"/>
         <v>46133</v>
@@ -3001,16 +3055,18 @@
       <c r="D24" s="4"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1">
+        <v>20</v>
+      </c>
+      <c r="K24" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C25" s="3">
         <f t="shared" si="1"/>
         <v>46134</v>
@@ -3018,16 +3074,18 @@
       <c r="D25" s="4"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1">
+        <v>20</v>
+      </c>
+      <c r="K25" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C26" s="3">
         <f t="shared" si="1"/>
         <v>46135</v>
@@ -3035,16 +3093,18 @@
       <c r="D26" s="4"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1">
+        <v>20</v>
+      </c>
+      <c r="K26" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C27" s="3">
         <f t="shared" si="1"/>
         <v>46136</v>
@@ -3052,16 +3112,18 @@
       <c r="D27" s="4"/>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1">
+        <v>20</v>
+      </c>
+      <c r="K27" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C28" s="3">
         <f t="shared" si="1"/>
         <v>46137</v>
@@ -3069,16 +3131,18 @@
       <c r="D28" s="4"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1">
+        <v>20</v>
+      </c>
+      <c r="K28" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C29" s="3">
         <f t="shared" si="1"/>
         <v>46138</v>
@@ -3086,16 +3150,18 @@
       <c r="D29" s="4"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1">
+        <v>20</v>
+      </c>
+      <c r="K29" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C30" s="3">
         <f t="shared" si="1"/>
         <v>46139</v>
@@ -3103,16 +3169,18 @@
       <c r="D30" s="4"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1">
+        <v>20</v>
+      </c>
+      <c r="K30" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C31" s="3">
         <f t="shared" si="1"/>
         <v>46140</v>
@@ -3120,16 +3188,18 @@
       <c r="D31" s="4"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1">
+        <v>20</v>
+      </c>
+      <c r="K31" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C32" s="3">
         <f t="shared" si="1"/>
         <v>46141</v>
@@ -3137,16 +3207,18 @@
       <c r="D32" s="4"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1">
+        <v>20</v>
+      </c>
+      <c r="K32" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C33" s="3">
         <f t="shared" si="1"/>
         <v>46142</v>
@@ -3154,16 +3226,18 @@
       <c r="D33" s="4"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1">
+        <v>20</v>
+      </c>
+      <c r="K33" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C34" s="3">
         <f t="shared" si="1"/>
         <v>46143</v>
@@ -3171,16 +3245,18 @@
       <c r="D34" s="4"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1">
+        <v>20</v>
+      </c>
+      <c r="K34" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="3:11" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
         <v>0</v>
@@ -3190,20 +3266,22 @@
         <v>0</v>
       </c>
       <c r="F36" s="5"/>
-      <c r="G36" s="1" t="e">
-        <f>AVERAGE(G4:G34)</f>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="1" t="e">
+        <f>AVERAGE(I4:I34)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
+      <c r="J36" s="1"/>
+      <c r="K36" s="5">
+        <f>AVERAGE(K4:K34)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="I3:K3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
@@ -3216,7 +3294,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
+  <conditionalFormatting sqref="I4:I34">
     <cfRule type="cellIs" dxfId="56" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
@@ -3242,19 +3320,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="29"/>
+      <c r="D3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="30"/>
       <c r="F3" s="17"/>
-      <c r="G3" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
+      <c r="G3" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -3967,19 +4045,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="29"/>
+      <c r="D3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="30"/>
       <c r="F3" s="16"/>
-      <c r="G3" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
+      <c r="G3" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -4694,19 +4772,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="29"/>
+      <c r="D3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="30"/>
       <c r="F3" s="15"/>
-      <c r="G3" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
+      <c r="G3" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -5400,19 +5478,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="29"/>
+      <c r="D3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="30"/>
       <c r="F3" s="14"/>
-      <c r="G3" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
+      <c r="G3" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -6133,19 +6211,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="29"/>
+      <c r="D3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="30"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
+      <c r="G3" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -6848,19 +6926,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="29"/>
+      <c r="D3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="30"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
+      <c r="G3" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -7587,19 +7665,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="29"/>
+      <c r="D3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="30"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
+      <c r="G3" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -8338,19 +8416,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="29"/>
+      <c r="D3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="30"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
+      <c r="G3" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -9065,19 +9143,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="29"/>
+      <c r="D3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="30"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
+      <c r="G3" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -9811,19 +9889,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="29"/>
+      <c r="D3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="30"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
+      <c r="G3" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -10492,19 +10570,19 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="29"/>
+      <c r="D3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="30"/>
       <c r="F3" s="28"/>
-      <c r="G3" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
+      <c r="G3" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
       <c r="K3" s="1" t="s">
         <v>32</v>
       </c>
@@ -11108,16 +11186,20 @@
         <f t="shared" si="1"/>
         <v>46293</v>
       </c>
-      <c r="D31" s="4"/>
+      <c r="D31" s="4">
+        <v>1</v>
+      </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
-      <c r="G31" s="1"/>
+      <c r="G31" s="1">
+        <v>15</v>
+      </c>
       <c r="H31" s="1">
         <v>20</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="32" spans="3:9" x14ac:dyDescent="0.3">
@@ -11157,21 +11239,21 @@
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E35" s="5">
         <f>D35/30</f>
-        <v>0.3</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>12.037037037037036</v>
+        <v>12.142857142857142</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.54166666666666674</v>
+        <v>0.56666666666666676</v>
       </c>
     </row>
   </sheetData>
@@ -11213,16 +11295,16 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="1"/>
-      <c r="C2" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="29"/>
+      <c r="C2" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="30"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
+      <c r="F2" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="3">
@@ -11908,19 +11990,19 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="29"/>
+      <c r="D3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="30"/>
       <c r="F3" s="27"/>
-      <c r="G3" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
+      <c r="G3" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
       <c r="K3" s="1" t="s">
         <v>32</v>
       </c>
@@ -12841,19 +12923,19 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="29"/>
+      <c r="D3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="30"/>
       <c r="F3" s="24"/>
-      <c r="G3" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
+      <c r="G3" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
       <c r="K3" s="1" t="s">
         <v>32</v>
       </c>
@@ -13954,19 +14036,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="29"/>
+      <c r="D3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="30"/>
       <c r="F3" s="22"/>
-      <c r="G3" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
+      <c r="G3" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -14669,19 +14751,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="29"/>
+      <c r="D3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="30"/>
       <c r="F3" s="21"/>
-      <c r="G3" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
+      <c r="G3" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -15399,19 +15481,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="29"/>
+      <c r="D3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="30"/>
       <c r="F3" s="20"/>
-      <c r="G3" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
+      <c r="G3" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -16105,19 +16187,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="29"/>
+      <c r="D3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="30"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
+      <c r="G3" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -16832,19 +16914,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="29"/>
+      <c r="D3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="30"/>
       <c r="F3" s="18"/>
-      <c r="G3" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
+      <c r="G3" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2619,7 +2619,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="30" t="s">
@@ -3320,7 +3320,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="30" t="s">
@@ -4045,7 +4045,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="30" t="s">
@@ -4772,7 +4772,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="30" t="s">
@@ -5478,7 +5478,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="30" t="s">
@@ -6211,7 +6211,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="30" t="s">
@@ -6926,7 +6926,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="30" t="s">
@@ -7665,7 +7665,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="30" t="s">
@@ -8416,7 +8416,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="30" t="s">
@@ -9143,7 +9143,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="30" t="s">
@@ -9889,7 +9889,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="30" t="s">
@@ -10570,7 +10570,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="30" t="s">
@@ -11207,16 +11207,20 @@
         <f t="shared" si="1"/>
         <v>46294</v>
       </c>
-      <c r="D32" s="4"/>
+      <c r="D32" s="4">
+        <v>1</v>
+      </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
-      <c r="G32" s="1"/>
+      <c r="G32" s="1">
+        <v>12</v>
+      </c>
       <c r="H32" s="1">
         <v>20</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="33" spans="3:9" x14ac:dyDescent="0.3">
@@ -11239,21 +11243,21 @@
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E35" s="5">
         <f>D35/30</f>
-        <v>0.33333333333333331</v>
+        <v>0.36666666666666664</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>12.142857142857142</v>
+        <v>12.137931034482758</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.56666666666666676</v>
+        <v>0.58666666666666678</v>
       </c>
     </row>
   </sheetData>
@@ -11990,7 +11994,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="30" t="s">
@@ -12923,7 +12927,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="30" t="s">
@@ -14036,7 +14040,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="30" t="s">
@@ -14751,7 +14755,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="30" t="s">
@@ -15481,7 +15485,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="30" t="s">
@@ -16187,7 +16191,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="30" t="s">
@@ -16914,7 +16918,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="30" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -13,25 +13,26 @@
   </bookViews>
   <sheets>
     <sheet name="_Base" sheetId="2" r:id="rId1"/>
-    <sheet name="2026-09" sheetId="21" r:id="rId2"/>
-    <sheet name="2026-08" sheetId="20" r:id="rId3"/>
-    <sheet name="2026-07" sheetId="19" r:id="rId4"/>
-    <sheet name="2026-06" sheetId="18" r:id="rId5"/>
-    <sheet name="2026-05" sheetId="17" r:id="rId6"/>
-    <sheet name="2026-04" sheetId="16" r:id="rId7"/>
-    <sheet name="2026-03" sheetId="15" r:id="rId8"/>
-    <sheet name="2026-02" sheetId="14" r:id="rId9"/>
-    <sheet name="2026-01" sheetId="13" r:id="rId10"/>
-    <sheet name="2025-12" sheetId="12" r:id="rId11"/>
-    <sheet name="2025-11" sheetId="11" r:id="rId12"/>
-    <sheet name="2025-10" sheetId="10" r:id="rId13"/>
-    <sheet name="2025-09" sheetId="9" r:id="rId14"/>
-    <sheet name="2025-08" sheetId="8" r:id="rId15"/>
-    <sheet name="2025-07" sheetId="7" r:id="rId16"/>
-    <sheet name="2025-06" sheetId="6" r:id="rId17"/>
-    <sheet name="2025-05" sheetId="5" r:id="rId18"/>
-    <sheet name="2025-04" sheetId="4" r:id="rId19"/>
-    <sheet name="2025-03" sheetId="1" r:id="rId20"/>
+    <sheet name="2026-10" sheetId="22" r:id="rId2"/>
+    <sheet name="2026-09" sheetId="21" r:id="rId3"/>
+    <sheet name="2026-08" sheetId="20" r:id="rId4"/>
+    <sheet name="2026-07" sheetId="19" r:id="rId5"/>
+    <sheet name="2026-06" sheetId="18" r:id="rId6"/>
+    <sheet name="2026-05" sheetId="17" r:id="rId7"/>
+    <sheet name="2026-04" sheetId="16" r:id="rId8"/>
+    <sheet name="2026-03" sheetId="15" r:id="rId9"/>
+    <sheet name="2026-02" sheetId="14" r:id="rId10"/>
+    <sheet name="2026-01" sheetId="13" r:id="rId11"/>
+    <sheet name="2025-12" sheetId="12" r:id="rId12"/>
+    <sheet name="2025-11" sheetId="11" r:id="rId13"/>
+    <sheet name="2025-10" sheetId="10" r:id="rId14"/>
+    <sheet name="2025-09" sheetId="9" r:id="rId15"/>
+    <sheet name="2025-08" sheetId="8" r:id="rId16"/>
+    <sheet name="2025-07" sheetId="7" r:id="rId17"/>
+    <sheet name="2025-06" sheetId="6" r:id="rId18"/>
+    <sheet name="2025-05" sheetId="5" r:id="rId19"/>
+    <sheet name="2025-04" sheetId="4" r:id="rId20"/>
+    <sheet name="2025-03" sheetId="1" r:id="rId21"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -1293,7 +1294,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="38">
   <si>
     <t>매일 운동하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1519,7 +1520,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1529,6 +1530,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1562,7 +1569,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1656,11 +1663,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="59">
+  <dxfs count="62">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2619,23 +2662,23 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="30"/>
+      <c r="D3" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="31"/>
       <c r="F3" s="29"/>
       <c r="G3" s="2" t="s">
         <v>37</v>
       </c>
       <c r="H3" s="29"/>
-      <c r="I3" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
+      <c r="I3" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
       <c r="M3" s="1" t="s">
         <v>32</v>
       </c>
@@ -3285,17 +3328,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="58" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="57" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="60" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4:I34">
-    <cfRule type="cellIs" dxfId="56" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="59" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3304,6 +3347,670 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:I33"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46296</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="31"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>46054</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>10</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>46055</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>12</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I31" si="0">G5/H5</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C31" si="1">C5+1</f>
+        <v>46056</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>14</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>46057</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>10</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>46058</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>12</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>46059</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>12</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>46060</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>8</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>46061</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>12</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>46062</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>12</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>46063</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>11</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>46064</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>10</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>46065</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>14</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>46066</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>12</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>46067</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>8</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>46068</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>12</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>46069</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>8</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>46070</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>8</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>46071</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>9</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>46072</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>12</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>46073</v>
+      </c>
+      <c r="D23" s="4">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>13</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>46074</v>
+      </c>
+      <c r="D24" s="4">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>10</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>46075</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>11</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>46076</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>13</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>46077</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>13</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>46078</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>10</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>46079</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>13</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>46080</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>8</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>46081</v>
+      </c>
+      <c r="D31" s="4">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D33" s="4">
+        <f>SUM(D4:D31)</f>
+        <v>4</v>
+      </c>
+      <c r="E33" s="5">
+        <f>D33/28</f>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="F33" s="5"/>
+      <c r="G33" s="1">
+        <f>AVERAGE(G4:G31)</f>
+        <v>10.964285714285714</v>
+      </c>
+      <c r="H33" s="1"/>
+      <c r="I33" s="5">
+        <f>AVERAGE(I4:I31)</f>
+        <v>0.54821428571428577</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C31">
+    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D31">
+    <cfRule type="cellIs" dxfId="36" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G31">
+    <cfRule type="cellIs" dxfId="35" priority="3" operator="greaterThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -3320,19 +4027,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="30"/>
+      <c r="D3" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="31"/>
       <c r="F3" s="17"/>
-      <c r="G3" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
+      <c r="G3" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -4000,6 +4707,733 @@
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
         <v>0.54838709677419339</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="32" priority="3" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:I36"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46296</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="31"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>45992</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>45993</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>10</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>45994</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>8</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>45995</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>8</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>45996</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>45997</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>45998</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>45999</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>11</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>46000</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>46001</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>11</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>46002</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>12</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>46003</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>10</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>46004</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>8</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>46005</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>10</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>46006</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>10</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>46007</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>46008</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>10</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>46009</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>10</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>46010</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>10</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>46011</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>11</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>46012</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>8</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>46013</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>12</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>46014</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>11</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>46015</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>11</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>46016</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>8</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>46017</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>9</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>46018</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>6</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>46019</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>46020</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1">
+        <v>12</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>46021</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>12</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>46022</v>
+      </c>
+      <c r="D34" s="4">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1">
+        <v>8</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>7</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0.22580645161290322</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>9.935483870967742</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0.49677419354838714</v>
       </c>
     </row>
   </sheetData>
@@ -4028,734 +5462,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:I36"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46295</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="30"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>45992</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>45993</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>10</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>45994</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>8</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>45995</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>8</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>45996</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>10</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>45997</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>10</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>45998</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>10</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>45999</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>11</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>46000</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>10</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>46001</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>11</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>46002</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>12</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>46003</v>
-      </c>
-      <c r="D15" s="4">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>10</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>46004</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>8</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>46005</v>
-      </c>
-      <c r="D17" s="4">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>10</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>46006</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>10</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>46007</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>10</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>46008</v>
-      </c>
-      <c r="D20" s="4">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>10</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>46009</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>10</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>46010</v>
-      </c>
-      <c r="D22" s="4">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>10</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>46011</v>
-      </c>
-      <c r="D23" s="4">
-        <v>2</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>11</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>46012</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>8</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>46013</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>12</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>46014</v>
-      </c>
-      <c r="D26" s="4">
-        <v>1</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>11</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>46015</v>
-      </c>
-      <c r="D27" s="4">
-        <v>0</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>11</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>46016</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>8</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>46017</v>
-      </c>
-      <c r="D29" s="4">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>9</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>46018</v>
-      </c>
-      <c r="D30" s="4">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>6</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>46019</v>
-      </c>
-      <c r="D31" s="4">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>10</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
-        <f t="shared" si="1"/>
-        <v>46020</v>
-      </c>
-      <c r="D32" s="4">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1">
-        <v>12</v>
-      </c>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="3">
-        <f t="shared" si="1"/>
-        <v>46021</v>
-      </c>
-      <c r="D33" s="4">
-        <v>0</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1">
-        <v>12</v>
-      </c>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
-        <f t="shared" si="1"/>
-        <v>46022</v>
-      </c>
-      <c r="D34" s="4">
-        <v>0</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1">
-        <v>8</v>
-      </c>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D36" s="4">
-        <f>SUM(D4:D34)</f>
-        <v>7</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/31</f>
-        <v>0.22580645161290322</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1">
-        <f>AVERAGE(G4:G34)</f>
-        <v>9.935483870967742</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
-        <v>0.49677419354838714</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="26" priority="3" operator="greaterThan">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -4772,19 +5479,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="30"/>
+      <c r="D3" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="31"/>
       <c r="F3" s="15"/>
-      <c r="G3" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
+      <c r="G3" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -5442,17 +6149,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="23" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="3" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5461,7 +6168,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -5478,19 +6185,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="30"/>
+      <c r="D3" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="31"/>
       <c r="F3" s="14"/>
-      <c r="G3" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
+      <c r="G3" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -6175,17 +6882,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="20" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="23" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6194,7 +6901,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -6211,19 +6918,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="30"/>
+      <c r="D3" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="31"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
+      <c r="G3" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -6890,17 +7597,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="18" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="17" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="3" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6909,7 +7616,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -6926,19 +7633,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="30"/>
+      <c r="D3" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="31"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
+      <c r="G3" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -7617,6 +8324,760 @@
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
         <v>0.44838709677419353</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="17" priority="3" operator="greaterThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:J40"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.25" customWidth="1"/>
+    <col min="6" max="6" width="5.25" customWidth="1"/>
+    <col min="7" max="9" width="8.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46296</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="31"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>45839</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>45840</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>8</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>45841</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>45842</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>9</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>45843</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>12</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>45844</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="J9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>45845</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>9</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>45846</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>9</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>45847</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>11</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>45848</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>14</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+      <c r="J13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>45849</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>12</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>45850</v>
+      </c>
+      <c r="D15" s="4">
+        <v>2</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>11</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>45851</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>10</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>45852</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>9</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>45853</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>16</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="J18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>45854</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>8</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>45855</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>13</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>45856</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>9</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>45857</v>
+      </c>
+      <c r="D22" s="4">
+        <v>2</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>9</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>45858</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>8</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="J23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>45859</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>9</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>45860</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>9</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>45861</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>11</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>45862</v>
+      </c>
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>8</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>45863</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>8</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>45864</v>
+      </c>
+      <c r="D29" s="4">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>10</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>45865</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>10</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>45866</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>45867</v>
+      </c>
+      <c r="D32" s="4">
+        <v>2</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1">
+        <v>10</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>45868</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>8</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>45869</v>
+      </c>
+      <c r="D34" s="4">
+        <v>1</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1">
+        <v>11</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>27</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0.87096774193548387</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>10.096774193548388</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0.50483870967741939</v>
+      </c>
+    </row>
+    <row r="39" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="E39" s="8"/>
+    </row>
+    <row r="40" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="E40" s="8">
+        <f>SUM(D4:D34)/31</f>
+        <v>0.87096774193548387</v>
       </c>
     </row>
   </sheetData>
@@ -7645,761 +9106,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:J40"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="8.25" customWidth="1"/>
-    <col min="6" max="6" width="5.25" customWidth="1"/>
-    <col min="7" max="9" width="8.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46295</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="30"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>45839</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>45840</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>8</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>45841</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>10</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>45842</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>9</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>45843</v>
-      </c>
-      <c r="D8" s="4">
-        <v>2</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>12</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>45844</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>10</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="J9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>45845</v>
-      </c>
-      <c r="D10" s="4">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>9</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>45846</v>
-      </c>
-      <c r="D11" s="4">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>9</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>45847</v>
-      </c>
-      <c r="D12" s="4">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>11</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>45848</v>
-      </c>
-      <c r="D13" s="4">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>14</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-      <c r="J13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>45849</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>12</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>45850</v>
-      </c>
-      <c r="D15" s="4">
-        <v>2</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>11</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>45851</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>10</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>45852</v>
-      </c>
-      <c r="D17" s="4">
-        <v>1</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>9</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>45853</v>
-      </c>
-      <c r="D18" s="4">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>16</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="J18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>45854</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>8</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>45855</v>
-      </c>
-      <c r="D20" s="4">
-        <v>1</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>13</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>45856</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>9</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>45857</v>
-      </c>
-      <c r="D22" s="4">
-        <v>2</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>9</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>45858</v>
-      </c>
-      <c r="D23" s="4">
-        <v>2</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>8</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-      <c r="J23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>45859</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>9</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>45860</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>9</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>45861</v>
-      </c>
-      <c r="D26" s="4">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>11</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>45862</v>
-      </c>
-      <c r="D27" s="4">
-        <v>1</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>8</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>45863</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>8</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>45864</v>
-      </c>
-      <c r="D29" s="4">
-        <v>1</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>10</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>45865</v>
-      </c>
-      <c r="D30" s="4">
-        <v>0</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>10</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>45866</v>
-      </c>
-      <c r="D31" s="4">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>10</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
-        <f t="shared" si="1"/>
-        <v>45867</v>
-      </c>
-      <c r="D32" s="4">
-        <v>2</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1">
-        <v>10</v>
-      </c>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="3">
-        <f t="shared" si="1"/>
-        <v>45868</v>
-      </c>
-      <c r="D33" s="4">
-        <v>1</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1">
-        <v>8</v>
-      </c>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
-        <f t="shared" si="1"/>
-        <v>45869</v>
-      </c>
-      <c r="D34" s="4">
-        <v>1</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1">
-        <v>11</v>
-      </c>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D36" s="4">
-        <f>SUM(D4:D34)</f>
-        <v>27</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/31</f>
-        <v>0.87096774193548387</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1">
-        <f>AVERAGE(G4:G34)</f>
-        <v>10.096774193548388</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
-        <v>0.50483870967741939</v>
-      </c>
-    </row>
-    <row r="39" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="E39" s="8"/>
-    </row>
-    <row r="40" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="E40" s="8">
-        <f>SUM(D4:D34)/31</f>
-        <v>0.87096774193548387</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -8416,19 +9123,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="30"/>
+      <c r="D3" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="31"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
+      <c r="G3" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -9107,17 +9814,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9126,7 +9833,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -9143,19 +9850,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="30"/>
+      <c r="D3" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="31"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
+      <c r="G3" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -9852,17 +10559,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9872,7 +10579,717 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:W36"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="0.75" customWidth="1"/>
+    <col min="7" max="7" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="0.75" customWidth="1"/>
+    <col min="13" max="13" width="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.25" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="0.875" customWidth="1"/>
+    <col min="21" max="23" width="4" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46296</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="31"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="30"/>
+      <c r="I3" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="M3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>46296</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1">
+        <v>20</v>
+      </c>
+      <c r="K4" s="5">
+        <f>I4/J4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>46297</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1">
+        <v>20</v>
+      </c>
+      <c r="K5" s="5">
+        <f t="shared" ref="K5:K34" si="0">I5/J5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>46298</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1">
+        <v>20</v>
+      </c>
+      <c r="K6" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>46299</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1">
+        <v>20</v>
+      </c>
+      <c r="K7" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>46300</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1">
+        <v>20</v>
+      </c>
+      <c r="K8" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>46301</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1">
+        <v>20</v>
+      </c>
+      <c r="K9" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>46302</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1">
+        <v>20</v>
+      </c>
+      <c r="K10" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>46303</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1">
+        <v>20</v>
+      </c>
+      <c r="K11" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>46304</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1">
+        <v>20</v>
+      </c>
+      <c r="K12" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>46305</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1">
+        <v>20</v>
+      </c>
+      <c r="K13" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>46306</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1">
+        <v>20</v>
+      </c>
+      <c r="K14" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>46307</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1">
+        <v>20</v>
+      </c>
+      <c r="K15" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>46308</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1">
+        <v>20</v>
+      </c>
+      <c r="K16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>46309</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1">
+        <v>20</v>
+      </c>
+      <c r="K17" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>46310</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1">
+        <v>20</v>
+      </c>
+      <c r="K18" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>46311</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1">
+        <v>20</v>
+      </c>
+      <c r="K19" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>46312</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1">
+        <v>20</v>
+      </c>
+      <c r="K20" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>46313</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1">
+        <v>20</v>
+      </c>
+      <c r="K21" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>46314</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1">
+        <v>20</v>
+      </c>
+      <c r="K22" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>46315</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1">
+        <v>20</v>
+      </c>
+      <c r="K23" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>46316</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1">
+        <v>20</v>
+      </c>
+      <c r="K24" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>46317</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1">
+        <v>20</v>
+      </c>
+      <c r="K25" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>46318</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1">
+        <v>20</v>
+      </c>
+      <c r="K26" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>46319</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1">
+        <v>20</v>
+      </c>
+      <c r="K27" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>46320</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1">
+        <v>20</v>
+      </c>
+      <c r="K28" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>46321</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1">
+        <v>20</v>
+      </c>
+      <c r="K29" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>46322</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1">
+        <v>20</v>
+      </c>
+      <c r="K30" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>46323</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1">
+        <v>20</v>
+      </c>
+      <c r="K31" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>46324</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1">
+        <v>20</v>
+      </c>
+      <c r="K32" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>46325</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1">
+        <v>20</v>
+      </c>
+      <c r="K33" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>46326</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1">
+        <v>20</v>
+      </c>
+      <c r="K34" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="1" t="e">
+        <f>AVERAGE(I4:I34)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J36" s="1"/>
+      <c r="K36" s="5">
+        <f>AVERAGE(K4:K34)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="I3:K3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4:I34">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I34"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -9889,19 +11306,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="30"/>
+      <c r="D3" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="31"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
+      <c r="G3" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -10530,17 +11947,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
       <formula>12</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10548,7 +11965,690 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:H35"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.875" customWidth="1"/>
+    <col min="5" max="5" width="1.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B2" s="1"/>
+      <c r="C2" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="31"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B3" s="3">
+        <v>45717</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="1">
+        <v>18</v>
+      </c>
+      <c r="G3" s="1">
+        <v>20</v>
+      </c>
+      <c r="H3" s="5">
+        <f>F3/G3</f>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="3">
+        <v>45718</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="1">
+        <v>13</v>
+      </c>
+      <c r="G4" s="1">
+        <v>20</v>
+      </c>
+      <c r="H4" s="5">
+        <f t="shared" ref="H4:H33" si="0">F4/G4</f>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="3">
+        <v>45719</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="1">
+        <v>12</v>
+      </c>
+      <c r="G5" s="1">
+        <v>20</v>
+      </c>
+      <c r="H5" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="3">
+        <v>45720</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="1">
+        <v>17</v>
+      </c>
+      <c r="G6" s="1">
+        <v>20</v>
+      </c>
+      <c r="H6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="3">
+        <v>45721</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="1">
+        <v>15</v>
+      </c>
+      <c r="G7" s="1">
+        <v>20</v>
+      </c>
+      <c r="H7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B8" s="3">
+        <v>45722</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="1">
+        <v>15</v>
+      </c>
+      <c r="G8" s="1">
+        <v>20</v>
+      </c>
+      <c r="H8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B9" s="3">
+        <v>45723</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="1">
+        <v>14</v>
+      </c>
+      <c r="G9" s="1">
+        <v>20</v>
+      </c>
+      <c r="H9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="3">
+        <v>45724</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="1">
+        <v>18</v>
+      </c>
+      <c r="G10" s="1">
+        <v>20</v>
+      </c>
+      <c r="H10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="3">
+        <v>45725</v>
+      </c>
+      <c r="C11" s="4">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="1">
+        <v>13</v>
+      </c>
+      <c r="G11" s="1">
+        <v>20</v>
+      </c>
+      <c r="H11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="3">
+        <v>45726</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="1">
+        <v>15</v>
+      </c>
+      <c r="G12" s="1">
+        <v>20</v>
+      </c>
+      <c r="H12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="3">
+        <v>45727</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="1">
+        <v>13</v>
+      </c>
+      <c r="G13" s="1">
+        <v>20</v>
+      </c>
+      <c r="H13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B14" s="3">
+        <v>45728</v>
+      </c>
+      <c r="C14" s="4">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="1">
+        <v>16</v>
+      </c>
+      <c r="G14" s="1">
+        <v>20</v>
+      </c>
+      <c r="H14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="3">
+        <v>45729</v>
+      </c>
+      <c r="C15" s="4">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="1">
+        <v>14</v>
+      </c>
+      <c r="G15" s="1">
+        <v>20</v>
+      </c>
+      <c r="H15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="3">
+        <v>45730</v>
+      </c>
+      <c r="C16" s="4">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="1">
+        <v>14</v>
+      </c>
+      <c r="G16" s="1">
+        <v>20</v>
+      </c>
+      <c r="H16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B17" s="3">
+        <v>45731</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="1">
+        <v>14</v>
+      </c>
+      <c r="G17" s="1">
+        <v>20</v>
+      </c>
+      <c r="H17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B18" s="3">
+        <v>45732</v>
+      </c>
+      <c r="C18" s="4">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="1">
+        <v>10</v>
+      </c>
+      <c r="G18" s="1">
+        <v>20</v>
+      </c>
+      <c r="H18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B19" s="3">
+        <v>45733</v>
+      </c>
+      <c r="C19" s="4">
+        <v>1</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="1">
+        <v>15</v>
+      </c>
+      <c r="G19" s="1">
+        <v>20</v>
+      </c>
+      <c r="H19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B20" s="3">
+        <v>45734</v>
+      </c>
+      <c r="C20" s="4">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="1">
+        <v>13</v>
+      </c>
+      <c r="G20" s="1">
+        <v>20</v>
+      </c>
+      <c r="H20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B21" s="3">
+        <v>45735</v>
+      </c>
+      <c r="C21" s="4">
+        <v>1</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="1">
+        <v>13</v>
+      </c>
+      <c r="G21" s="1">
+        <v>20</v>
+      </c>
+      <c r="H21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B22" s="3">
+        <v>45736</v>
+      </c>
+      <c r="C22" s="4">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="1">
+        <v>14</v>
+      </c>
+      <c r="G22" s="1">
+        <v>20</v>
+      </c>
+      <c r="H22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B23" s="3">
+        <v>45737</v>
+      </c>
+      <c r="C23" s="4">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="1">
+        <v>13</v>
+      </c>
+      <c r="G23" s="1">
+        <v>20</v>
+      </c>
+      <c r="H23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B24" s="3">
+        <v>45738</v>
+      </c>
+      <c r="C24" s="4">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="1">
+        <v>15</v>
+      </c>
+      <c r="G24" s="1">
+        <v>20</v>
+      </c>
+      <c r="H24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B25" s="3">
+        <v>45739</v>
+      </c>
+      <c r="C25" s="4">
+        <v>1</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="1">
+        <v>10</v>
+      </c>
+      <c r="G25" s="1">
+        <v>20</v>
+      </c>
+      <c r="H25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B26" s="3">
+        <v>45740</v>
+      </c>
+      <c r="C26" s="4">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="1">
+        <v>15</v>
+      </c>
+      <c r="G26" s="1">
+        <v>20</v>
+      </c>
+      <c r="H26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B27" s="3">
+        <v>45741</v>
+      </c>
+      <c r="C27" s="4">
+        <v>1</v>
+      </c>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="1">
+        <v>13</v>
+      </c>
+      <c r="G27" s="1">
+        <v>20</v>
+      </c>
+      <c r="H27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B28" s="3">
+        <v>45742</v>
+      </c>
+      <c r="C28" s="4">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="1">
+        <v>14</v>
+      </c>
+      <c r="G28" s="1">
+        <v>20</v>
+      </c>
+      <c r="H28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B29" s="3">
+        <v>45743</v>
+      </c>
+      <c r="C29" s="4">
+        <v>1</v>
+      </c>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="1">
+        <v>13</v>
+      </c>
+      <c r="G29" s="1">
+        <v>20</v>
+      </c>
+      <c r="H29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B30" s="3">
+        <v>45744</v>
+      </c>
+      <c r="C30" s="4">
+        <v>0</v>
+      </c>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="1">
+        <v>15</v>
+      </c>
+      <c r="G30" s="1">
+        <v>20</v>
+      </c>
+      <c r="H30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B31" s="3">
+        <v>45745</v>
+      </c>
+      <c r="C31" s="4">
+        <v>1</v>
+      </c>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="1">
+        <v>14</v>
+      </c>
+      <c r="G31" s="1">
+        <v>20</v>
+      </c>
+      <c r="H31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B32" s="3">
+        <v>45746</v>
+      </c>
+      <c r="C32" s="4">
+        <v>1</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="1">
+        <v>10</v>
+      </c>
+      <c r="G32" s="1">
+        <v>20</v>
+      </c>
+      <c r="H32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B33" s="3">
+        <v>45747</v>
+      </c>
+      <c r="C33" s="4">
+        <v>1</v>
+      </c>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="1">
+        <v>15</v>
+      </c>
+      <c r="G33" s="1">
+        <v>20</v>
+      </c>
+      <c r="H33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C35" s="4">
+        <f>SUM(C3:C33)</f>
+        <v>22</v>
+      </c>
+      <c r="D35" s="5">
+        <f>C35/31</f>
+        <v>0.70967741935483875</v>
+      </c>
+      <c r="E35" s="5"/>
+      <c r="F35" s="1">
+        <f>AVERAGE(F3:F33)</f>
+        <v>13.96774193548387</v>
+      </c>
+      <c r="G35" s="1"/>
+      <c r="H35" s="5">
+        <f>AVERAGE(H3:H33)</f>
+        <v>0.69838709677419342</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="C2:D2"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C3:C33">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F33">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
+      <formula>14</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:U35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -10570,19 +12670,19 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="30"/>
+      <c r="D3" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="31"/>
       <c r="F3" s="28"/>
-      <c r="G3" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
+      <c r="G3" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
       <c r="K3" s="1" t="s">
         <v>32</v>
       </c>
@@ -11228,36 +13328,40 @@
         <f t="shared" si="1"/>
         <v>46295</v>
       </c>
-      <c r="D33" s="4"/>
+      <c r="D33" s="4">
+        <v>1</v>
+      </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
-      <c r="G33" s="1"/>
+      <c r="G33" s="1">
+        <v>14</v>
+      </c>
       <c r="H33" s="1">
         <v>20</v>
       </c>
       <c r="I33" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E35" s="5">
         <f>D35/30</f>
-        <v>0.36666666666666664</v>
+        <v>0.4</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>12.137931034482758</v>
+        <v>12.2</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.58666666666666678</v>
+        <v>0.6100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -11267,17 +13371,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="55" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="54" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="57" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="53" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="56" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11287,690 +13391,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:H35"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.875" customWidth="1"/>
-    <col min="5" max="5" width="1.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B2" s="1"/>
-      <c r="C2" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B3" s="3">
-        <v>45717</v>
-      </c>
-      <c r="C3" s="4">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="1">
-        <v>18</v>
-      </c>
-      <c r="G3" s="1">
-        <v>20</v>
-      </c>
-      <c r="H3" s="5">
-        <f>F3/G3</f>
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B4" s="3">
-        <v>45718</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="1">
-        <v>13</v>
-      </c>
-      <c r="G4" s="1">
-        <v>20</v>
-      </c>
-      <c r="H4" s="5">
-        <f t="shared" ref="H4:H33" si="0">F4/G4</f>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B5" s="3">
-        <v>45719</v>
-      </c>
-      <c r="C5" s="4">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="1">
-        <v>12</v>
-      </c>
-      <c r="G5" s="1">
-        <v>20</v>
-      </c>
-      <c r="H5" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B6" s="3">
-        <v>45720</v>
-      </c>
-      <c r="C6" s="4">
-        <v>1</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="1">
-        <v>17</v>
-      </c>
-      <c r="G6" s="1">
-        <v>20</v>
-      </c>
-      <c r="H6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B7" s="3">
-        <v>45721</v>
-      </c>
-      <c r="C7" s="4">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="1">
-        <v>15</v>
-      </c>
-      <c r="G7" s="1">
-        <v>20</v>
-      </c>
-      <c r="H7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B8" s="3">
-        <v>45722</v>
-      </c>
-      <c r="C8" s="4">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="1">
-        <v>15</v>
-      </c>
-      <c r="G8" s="1">
-        <v>20</v>
-      </c>
-      <c r="H8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B9" s="3">
-        <v>45723</v>
-      </c>
-      <c r="C9" s="4">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="1">
-        <v>14</v>
-      </c>
-      <c r="G9" s="1">
-        <v>20</v>
-      </c>
-      <c r="H9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B10" s="3">
-        <v>45724</v>
-      </c>
-      <c r="C10" s="4">
-        <v>1</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="1">
-        <v>18</v>
-      </c>
-      <c r="G10" s="1">
-        <v>20</v>
-      </c>
-      <c r="H10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="3">
-        <v>45725</v>
-      </c>
-      <c r="C11" s="4">
-        <v>0</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="1">
-        <v>13</v>
-      </c>
-      <c r="G11" s="1">
-        <v>20</v>
-      </c>
-      <c r="H11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B12" s="3">
-        <v>45726</v>
-      </c>
-      <c r="C12" s="4">
-        <v>1</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="1">
-        <v>15</v>
-      </c>
-      <c r="G12" s="1">
-        <v>20</v>
-      </c>
-      <c r="H12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="3">
-        <v>45727</v>
-      </c>
-      <c r="C13" s="4">
-        <v>1</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="1">
-        <v>13</v>
-      </c>
-      <c r="G13" s="1">
-        <v>20</v>
-      </c>
-      <c r="H13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B14" s="3">
-        <v>45728</v>
-      </c>
-      <c r="C14" s="4">
-        <v>1</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="1">
-        <v>16</v>
-      </c>
-      <c r="G14" s="1">
-        <v>20</v>
-      </c>
-      <c r="H14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B15" s="3">
-        <v>45729</v>
-      </c>
-      <c r="C15" s="4">
-        <v>0</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="1">
-        <v>14</v>
-      </c>
-      <c r="G15" s="1">
-        <v>20</v>
-      </c>
-      <c r="H15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B16" s="3">
-        <v>45730</v>
-      </c>
-      <c r="C16" s="4">
-        <v>0</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="1">
-        <v>14</v>
-      </c>
-      <c r="G16" s="1">
-        <v>20</v>
-      </c>
-      <c r="H16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="3">
-        <v>45731</v>
-      </c>
-      <c r="C17" s="4">
-        <v>1</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="1">
-        <v>14</v>
-      </c>
-      <c r="G17" s="1">
-        <v>20</v>
-      </c>
-      <c r="H17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B18" s="3">
-        <v>45732</v>
-      </c>
-      <c r="C18" s="4">
-        <v>0</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="1">
-        <v>10</v>
-      </c>
-      <c r="G18" s="1">
-        <v>20</v>
-      </c>
-      <c r="H18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B19" s="3">
-        <v>45733</v>
-      </c>
-      <c r="C19" s="4">
-        <v>1</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="1">
-        <v>15</v>
-      </c>
-      <c r="G19" s="1">
-        <v>20</v>
-      </c>
-      <c r="H19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="3">
-        <v>45734</v>
-      </c>
-      <c r="C20" s="4">
-        <v>1</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="1">
-        <v>13</v>
-      </c>
-      <c r="G20" s="1">
-        <v>20</v>
-      </c>
-      <c r="H20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B21" s="3">
-        <v>45735</v>
-      </c>
-      <c r="C21" s="4">
-        <v>1</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="1">
-        <v>13</v>
-      </c>
-      <c r="G21" s="1">
-        <v>20</v>
-      </c>
-      <c r="H21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B22" s="3">
-        <v>45736</v>
-      </c>
-      <c r="C22" s="4">
-        <v>1</v>
-      </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="1">
-        <v>14</v>
-      </c>
-      <c r="G22" s="1">
-        <v>20</v>
-      </c>
-      <c r="H22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B23" s="3">
-        <v>45737</v>
-      </c>
-      <c r="C23" s="4">
-        <v>0</v>
-      </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="1">
-        <v>13</v>
-      </c>
-      <c r="G23" s="1">
-        <v>20</v>
-      </c>
-      <c r="H23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B24" s="3">
-        <v>45738</v>
-      </c>
-      <c r="C24" s="4">
-        <v>1</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="1">
-        <v>15</v>
-      </c>
-      <c r="G24" s="1">
-        <v>20</v>
-      </c>
-      <c r="H24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B25" s="3">
-        <v>45739</v>
-      </c>
-      <c r="C25" s="4">
-        <v>1</v>
-      </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="1">
-        <v>10</v>
-      </c>
-      <c r="G25" s="1">
-        <v>20</v>
-      </c>
-      <c r="H25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B26" s="3">
-        <v>45740</v>
-      </c>
-      <c r="C26" s="4">
-        <v>1</v>
-      </c>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="1">
-        <v>15</v>
-      </c>
-      <c r="G26" s="1">
-        <v>20</v>
-      </c>
-      <c r="H26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B27" s="3">
-        <v>45741</v>
-      </c>
-      <c r="C27" s="4">
-        <v>1</v>
-      </c>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="1">
-        <v>13</v>
-      </c>
-      <c r="G27" s="1">
-        <v>20</v>
-      </c>
-      <c r="H27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B28" s="3">
-        <v>45742</v>
-      </c>
-      <c r="C28" s="4">
-        <v>0</v>
-      </c>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="1">
-        <v>14</v>
-      </c>
-      <c r="G28" s="1">
-        <v>20</v>
-      </c>
-      <c r="H28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B29" s="3">
-        <v>45743</v>
-      </c>
-      <c r="C29" s="4">
-        <v>1</v>
-      </c>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="1">
-        <v>13</v>
-      </c>
-      <c r="G29" s="1">
-        <v>20</v>
-      </c>
-      <c r="H29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B30" s="3">
-        <v>45744</v>
-      </c>
-      <c r="C30" s="4">
-        <v>0</v>
-      </c>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="1">
-        <v>15</v>
-      </c>
-      <c r="G30" s="1">
-        <v>20</v>
-      </c>
-      <c r="H30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B31" s="3">
-        <v>45745</v>
-      </c>
-      <c r="C31" s="4">
-        <v>1</v>
-      </c>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="1">
-        <v>14</v>
-      </c>
-      <c r="G31" s="1">
-        <v>20</v>
-      </c>
-      <c r="H31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B32" s="3">
-        <v>45746</v>
-      </c>
-      <c r="C32" s="4">
-        <v>1</v>
-      </c>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="1">
-        <v>10</v>
-      </c>
-      <c r="G32" s="1">
-        <v>20</v>
-      </c>
-      <c r="H32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B33" s="3">
-        <v>45747</v>
-      </c>
-      <c r="C33" s="4">
-        <v>1</v>
-      </c>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="1">
-        <v>15</v>
-      </c>
-      <c r="G33" s="1">
-        <v>20</v>
-      </c>
-      <c r="H33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C35" s="4">
-        <f>SUM(C3:C33)</f>
-        <v>22</v>
-      </c>
-      <c r="D35" s="5">
-        <f>C35/31</f>
-        <v>0.70967741935483875</v>
-      </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="1">
-        <f>AVERAGE(F3:F33)</f>
-        <v>13.96774193548387</v>
-      </c>
-      <c r="G35" s="1"/>
-      <c r="H35" s="5">
-        <f>AVERAGE(H3:H33)</f>
-        <v>0.69838709677419342</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="C2:D2"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C3:C33">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F33">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
-      <formula>14</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:W36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -11994,19 +13415,19 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="30"/>
+      <c r="D3" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="31"/>
       <c r="F3" s="27"/>
-      <c r="G3" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
+      <c r="G3" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
       <c r="K3" s="1" t="s">
         <v>32</v>
       </c>
@@ -12875,6 +14296,1125 @@
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
         <v>0.59354838709677427</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="55" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="54" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="53" priority="3" operator="greaterThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:V36"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="0.875" customWidth="1"/>
+    <col min="19" max="21" width="5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46296</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="31"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="K3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>46204</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>8</v>
+      </c>
+      <c r="H4" s="26">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.4</v>
+      </c>
+      <c r="K4">
+        <v>150</v>
+      </c>
+      <c r="L4">
+        <v>162</v>
+      </c>
+      <c r="M4">
+        <v>158</v>
+      </c>
+      <c r="N4">
+        <v>157</v>
+      </c>
+      <c r="O4">
+        <v>159</v>
+      </c>
+      <c r="P4">
+        <v>162</v>
+      </c>
+      <c r="Q4">
+        <v>156</v>
+      </c>
+      <c r="S4">
+        <v>137</v>
+      </c>
+      <c r="T4">
+        <v>128</v>
+      </c>
+      <c r="U4">
+        <v>123</v>
+      </c>
+      <c r="V4" s="25">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="5" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>46205</v>
+      </c>
+      <c r="D5" s="4">
+        <v>2</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>10</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.5</v>
+      </c>
+      <c r="K5">
+        <v>157</v>
+      </c>
+      <c r="L5">
+        <v>159</v>
+      </c>
+      <c r="M5">
+        <v>156</v>
+      </c>
+      <c r="N5">
+        <v>161</v>
+      </c>
+      <c r="O5">
+        <v>158</v>
+      </c>
+      <c r="P5">
+        <v>157</v>
+      </c>
+      <c r="Q5">
+        <v>160</v>
+      </c>
+      <c r="S5">
+        <v>131</v>
+      </c>
+      <c r="T5">
+        <v>124</v>
+      </c>
+      <c r="U5">
+        <v>125</v>
+      </c>
+      <c r="V5" s="25">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="6" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>46206</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>46207</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>10</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>46208</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="K8">
+        <v>140</v>
+      </c>
+      <c r="L8">
+        <v>146</v>
+      </c>
+      <c r="M8">
+        <v>140</v>
+      </c>
+      <c r="N8">
+        <v>139</v>
+      </c>
+      <c r="S8">
+        <v>117</v>
+      </c>
+      <c r="T8">
+        <v>104</v>
+      </c>
+      <c r="U8">
+        <v>103</v>
+      </c>
+      <c r="V8" s="25">
+        <v>46208</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>46209</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>9</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+      <c r="K9">
+        <v>146</v>
+      </c>
+      <c r="L9">
+        <v>150</v>
+      </c>
+      <c r="M9">
+        <v>154</v>
+      </c>
+      <c r="N9">
+        <v>151</v>
+      </c>
+      <c r="O9">
+        <v>154</v>
+      </c>
+      <c r="P9">
+        <v>152</v>
+      </c>
+      <c r="Q9">
+        <v>156</v>
+      </c>
+      <c r="S9">
+        <v>130</v>
+      </c>
+      <c r="T9">
+        <v>122</v>
+      </c>
+      <c r="U9">
+        <v>116</v>
+      </c>
+      <c r="V9" s="25">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="10" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>46210</v>
+      </c>
+      <c r="D10" s="4">
+        <v>2</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="K10">
+        <v>151</v>
+      </c>
+      <c r="L10">
+        <v>157</v>
+      </c>
+      <c r="M10">
+        <v>155</v>
+      </c>
+      <c r="N10">
+        <v>154</v>
+      </c>
+      <c r="O10">
+        <v>151</v>
+      </c>
+      <c r="P10">
+        <v>154</v>
+      </c>
+      <c r="Q10">
+        <v>160</v>
+      </c>
+      <c r="S10">
+        <v>124</v>
+      </c>
+      <c r="T10">
+        <v>115</v>
+      </c>
+      <c r="U10">
+        <v>111</v>
+      </c>
+      <c r="V10" s="25">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="11" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>46211</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>10</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>46212</v>
+      </c>
+      <c r="D12" s="4">
+        <v>2</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>11</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="K12">
+        <v>154</v>
+      </c>
+      <c r="L12">
+        <v>156</v>
+      </c>
+      <c r="M12">
+        <v>152</v>
+      </c>
+      <c r="N12">
+        <v>153</v>
+      </c>
+      <c r="O12">
+        <v>150</v>
+      </c>
+      <c r="P12">
+        <v>151</v>
+      </c>
+      <c r="Q12">
+        <v>155</v>
+      </c>
+      <c r="S12">
+        <v>125</v>
+      </c>
+      <c r="T12">
+        <v>118</v>
+      </c>
+      <c r="U12">
+        <v>114</v>
+      </c>
+      <c r="V12" s="25">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="13" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>46213</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>9</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="14" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>46214</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>9</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>46215</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>12</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="16" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>46216</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>10</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>46217</v>
+      </c>
+      <c r="D17" s="4">
+        <v>2</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>10</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="K17">
+        <v>153</v>
+      </c>
+      <c r="L17">
+        <v>160</v>
+      </c>
+      <c r="M17">
+        <v>160</v>
+      </c>
+      <c r="N17">
+        <v>161</v>
+      </c>
+      <c r="O17">
+        <v>158</v>
+      </c>
+      <c r="P17">
+        <v>158</v>
+      </c>
+      <c r="Q17">
+        <v>160</v>
+      </c>
+      <c r="S17">
+        <v>132</v>
+      </c>
+      <c r="T17">
+        <v>122</v>
+      </c>
+      <c r="U17">
+        <v>122</v>
+      </c>
+      <c r="V17" s="25">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>46218</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>12</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>46219</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>12</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>46220</v>
+      </c>
+      <c r="D20" s="4">
+        <v>2</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>8</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="K20">
+        <v>149</v>
+      </c>
+      <c r="L20">
+        <v>155</v>
+      </c>
+      <c r="M20">
+        <v>159</v>
+      </c>
+      <c r="N20">
+        <v>159</v>
+      </c>
+      <c r="O20">
+        <v>162</v>
+      </c>
+      <c r="P20">
+        <v>168</v>
+      </c>
+      <c r="Q20">
+        <v>167</v>
+      </c>
+      <c r="S20">
+        <v>145</v>
+      </c>
+      <c r="T20">
+        <v>138</v>
+      </c>
+      <c r="U20">
+        <v>131</v>
+      </c>
+      <c r="V20" s="25">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>46221</v>
+      </c>
+      <c r="D21" s="4">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>12</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>46222</v>
+      </c>
+      <c r="D22" s="4">
+        <v>2</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>12</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+      <c r="K22">
+        <v>147</v>
+      </c>
+      <c r="L22">
+        <v>145</v>
+      </c>
+      <c r="M22">
+        <v>144</v>
+      </c>
+      <c r="N22">
+        <v>146</v>
+      </c>
+      <c r="O22">
+        <v>145</v>
+      </c>
+      <c r="P22">
+        <v>148</v>
+      </c>
+      <c r="Q22">
+        <v>150</v>
+      </c>
+      <c r="S22">
+        <v>124</v>
+      </c>
+      <c r="T22">
+        <v>118</v>
+      </c>
+      <c r="U22">
+        <v>114</v>
+      </c>
+      <c r="V22" s="25">
+        <v>46222</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>46223</v>
+      </c>
+      <c r="D23" s="4">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>12</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>46224</v>
+      </c>
+      <c r="D24" s="4">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>10</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>46225</v>
+      </c>
+      <c r="D25" s="4">
+        <v>1</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>12</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>46226</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>10</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>46227</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>9</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>46228</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>10</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>46229</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>9</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>46230</v>
+      </c>
+      <c r="D30" s="4">
+        <v>2</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>10</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="K30">
+        <v>153</v>
+      </c>
+      <c r="L30">
+        <v>156</v>
+      </c>
+      <c r="M30">
+        <v>164</v>
+      </c>
+      <c r="N30">
+        <v>158</v>
+      </c>
+      <c r="O30">
+        <v>156</v>
+      </c>
+      <c r="P30">
+        <v>160</v>
+      </c>
+      <c r="Q30">
+        <v>160</v>
+      </c>
+      <c r="S30">
+        <v>136</v>
+      </c>
+      <c r="T30">
+        <v>129</v>
+      </c>
+      <c r="U30">
+        <v>127</v>
+      </c>
+      <c r="V30" s="25">
+        <v>46230</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>46231</v>
+      </c>
+      <c r="D31" s="4">
+        <v>1</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>12</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+      <c r="K31">
+        <v>157</v>
+      </c>
+      <c r="L31">
+        <v>160</v>
+      </c>
+      <c r="M31">
+        <v>164</v>
+      </c>
+      <c r="N31">
+        <v>163</v>
+      </c>
+      <c r="O31">
+        <v>166</v>
+      </c>
+      <c r="P31">
+        <v>164</v>
+      </c>
+      <c r="Q31">
+        <v>162</v>
+      </c>
+      <c r="S31">
+        <v>138</v>
+      </c>
+      <c r="T31">
+        <v>133</v>
+      </c>
+      <c r="U31">
+        <v>127</v>
+      </c>
+      <c r="V31" s="25">
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>46232</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1">
+        <v>13</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>46233</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>14</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>46234</v>
+      </c>
+      <c r="D34" s="4">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1">
+        <v>12</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>21</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0.67741935483870963</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>10.548387096774194</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0.52741935483870961</v>
       </c>
     </row>
   </sheetData>
@@ -12904,1126 +15444,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:V36"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="0.875" customWidth="1"/>
-    <col min="19" max="21" width="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46295</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="30"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="K3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="R3" s="1"/>
-      <c r="S3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>46204</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>8</v>
-      </c>
-      <c r="H4" s="26">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0.4</v>
-      </c>
-      <c r="K4">
-        <v>150</v>
-      </c>
-      <c r="L4">
-        <v>162</v>
-      </c>
-      <c r="M4">
-        <v>158</v>
-      </c>
-      <c r="N4">
-        <v>157</v>
-      </c>
-      <c r="O4">
-        <v>159</v>
-      </c>
-      <c r="P4">
-        <v>162</v>
-      </c>
-      <c r="Q4">
-        <v>156</v>
-      </c>
-      <c r="S4">
-        <v>137</v>
-      </c>
-      <c r="T4">
-        <v>128</v>
-      </c>
-      <c r="U4">
-        <v>123</v>
-      </c>
-      <c r="V4" s="25">
-        <v>46201</v>
-      </c>
-    </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>46205</v>
-      </c>
-      <c r="D5" s="4">
-        <v>2</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>10</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0.5</v>
-      </c>
-      <c r="K5">
-        <v>157</v>
-      </c>
-      <c r="L5">
-        <v>159</v>
-      </c>
-      <c r="M5">
-        <v>156</v>
-      </c>
-      <c r="N5">
-        <v>161</v>
-      </c>
-      <c r="O5">
-        <v>158</v>
-      </c>
-      <c r="P5">
-        <v>157</v>
-      </c>
-      <c r="Q5">
-        <v>160</v>
-      </c>
-      <c r="S5">
-        <v>131</v>
-      </c>
-      <c r="T5">
-        <v>124</v>
-      </c>
-      <c r="U5">
-        <v>125</v>
-      </c>
-      <c r="V5" s="25">
-        <v>46205</v>
-      </c>
-    </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>46206</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>10</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>46207</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>10</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>46208</v>
-      </c>
-      <c r="D8" s="4">
-        <v>2</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>10</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="K8">
-        <v>140</v>
-      </c>
-      <c r="L8">
-        <v>146</v>
-      </c>
-      <c r="M8">
-        <v>140</v>
-      </c>
-      <c r="N8">
-        <v>139</v>
-      </c>
-      <c r="S8">
-        <v>117</v>
-      </c>
-      <c r="T8">
-        <v>104</v>
-      </c>
-      <c r="U8">
-        <v>103</v>
-      </c>
-      <c r="V8" s="25">
-        <v>46208</v>
-      </c>
-    </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>46209</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>9</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-      <c r="K9">
-        <v>146</v>
-      </c>
-      <c r="L9">
-        <v>150</v>
-      </c>
-      <c r="M9">
-        <v>154</v>
-      </c>
-      <c r="N9">
-        <v>151</v>
-      </c>
-      <c r="O9">
-        <v>154</v>
-      </c>
-      <c r="P9">
-        <v>152</v>
-      </c>
-      <c r="Q9">
-        <v>156</v>
-      </c>
-      <c r="S9">
-        <v>130</v>
-      </c>
-      <c r="T9">
-        <v>122</v>
-      </c>
-      <c r="U9">
-        <v>116</v>
-      </c>
-      <c r="V9" s="25">
-        <v>46209</v>
-      </c>
-    </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>46210</v>
-      </c>
-      <c r="D10" s="4">
-        <v>2</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>10</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="K10">
-        <v>151</v>
-      </c>
-      <c r="L10">
-        <v>157</v>
-      </c>
-      <c r="M10">
-        <v>155</v>
-      </c>
-      <c r="N10">
-        <v>154</v>
-      </c>
-      <c r="O10">
-        <v>151</v>
-      </c>
-      <c r="P10">
-        <v>154</v>
-      </c>
-      <c r="Q10">
-        <v>160</v>
-      </c>
-      <c r="S10">
-        <v>124</v>
-      </c>
-      <c r="T10">
-        <v>115</v>
-      </c>
-      <c r="U10">
-        <v>111</v>
-      </c>
-      <c r="V10" s="25">
-        <v>46210</v>
-      </c>
-    </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>46211</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>10</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>46212</v>
-      </c>
-      <c r="D12" s="4">
-        <v>2</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>11</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="K12">
-        <v>154</v>
-      </c>
-      <c r="L12">
-        <v>156</v>
-      </c>
-      <c r="M12">
-        <v>152</v>
-      </c>
-      <c r="N12">
-        <v>153</v>
-      </c>
-      <c r="O12">
-        <v>150</v>
-      </c>
-      <c r="P12">
-        <v>151</v>
-      </c>
-      <c r="Q12">
-        <v>155</v>
-      </c>
-      <c r="S12">
-        <v>125</v>
-      </c>
-      <c r="T12">
-        <v>118</v>
-      </c>
-      <c r="U12">
-        <v>114</v>
-      </c>
-      <c r="V12" s="25">
-        <v>46212</v>
-      </c>
-    </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>46213</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>9</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>46214</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>9</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>46215</v>
-      </c>
-      <c r="D15" s="4">
-        <v>1</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>12</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>46216</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>10</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>46217</v>
-      </c>
-      <c r="D17" s="4">
-        <v>2</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>10</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="K17">
-        <v>153</v>
-      </c>
-      <c r="L17">
-        <v>160</v>
-      </c>
-      <c r="M17">
-        <v>160</v>
-      </c>
-      <c r="N17">
-        <v>161</v>
-      </c>
-      <c r="O17">
-        <v>158</v>
-      </c>
-      <c r="P17">
-        <v>158</v>
-      </c>
-      <c r="Q17">
-        <v>160</v>
-      </c>
-      <c r="S17">
-        <v>132</v>
-      </c>
-      <c r="T17">
-        <v>122</v>
-      </c>
-      <c r="U17">
-        <v>122</v>
-      </c>
-      <c r="V17" s="25">
-        <v>46217</v>
-      </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>46218</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>12</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>46219</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>12</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>46220</v>
-      </c>
-      <c r="D20" s="4">
-        <v>2</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>8</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-      <c r="K20">
-        <v>149</v>
-      </c>
-      <c r="L20">
-        <v>155</v>
-      </c>
-      <c r="M20">
-        <v>159</v>
-      </c>
-      <c r="N20">
-        <v>159</v>
-      </c>
-      <c r="O20">
-        <v>162</v>
-      </c>
-      <c r="P20">
-        <v>168</v>
-      </c>
-      <c r="Q20">
-        <v>167</v>
-      </c>
-      <c r="S20">
-        <v>145</v>
-      </c>
-      <c r="T20">
-        <v>138</v>
-      </c>
-      <c r="U20">
-        <v>131</v>
-      </c>
-      <c r="V20" s="25">
-        <v>46220</v>
-      </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>46221</v>
-      </c>
-      <c r="D21" s="4">
-        <v>1</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>12</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>46222</v>
-      </c>
-      <c r="D22" s="4">
-        <v>2</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>12</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-      <c r="K22">
-        <v>147</v>
-      </c>
-      <c r="L22">
-        <v>145</v>
-      </c>
-      <c r="M22">
-        <v>144</v>
-      </c>
-      <c r="N22">
-        <v>146</v>
-      </c>
-      <c r="O22">
-        <v>145</v>
-      </c>
-      <c r="P22">
-        <v>148</v>
-      </c>
-      <c r="Q22">
-        <v>150</v>
-      </c>
-      <c r="S22">
-        <v>124</v>
-      </c>
-      <c r="T22">
-        <v>118</v>
-      </c>
-      <c r="U22">
-        <v>114</v>
-      </c>
-      <c r="V22" s="25">
-        <v>46222</v>
-      </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>46223</v>
-      </c>
-      <c r="D23" s="4">
-        <v>0</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>12</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>46224</v>
-      </c>
-      <c r="D24" s="4">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>10</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>46225</v>
-      </c>
-      <c r="D25" s="4">
-        <v>1</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>12</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>46226</v>
-      </c>
-      <c r="D26" s="4">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>10</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>46227</v>
-      </c>
-      <c r="D27" s="4">
-        <v>0</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>9</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>46228</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>10</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>46229</v>
-      </c>
-      <c r="D29" s="4">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>9</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>46230</v>
-      </c>
-      <c r="D30" s="4">
-        <v>2</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>10</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="K30">
-        <v>153</v>
-      </c>
-      <c r="L30">
-        <v>156</v>
-      </c>
-      <c r="M30">
-        <v>164</v>
-      </c>
-      <c r="N30">
-        <v>158</v>
-      </c>
-      <c r="O30">
-        <v>156</v>
-      </c>
-      <c r="P30">
-        <v>160</v>
-      </c>
-      <c r="Q30">
-        <v>160</v>
-      </c>
-      <c r="S30">
-        <v>136</v>
-      </c>
-      <c r="T30">
-        <v>129</v>
-      </c>
-      <c r="U30">
-        <v>127</v>
-      </c>
-      <c r="V30" s="25">
-        <v>46230</v>
-      </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>46231</v>
-      </c>
-      <c r="D31" s="4">
-        <v>1</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>12</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-      <c r="K31">
-        <v>157</v>
-      </c>
-      <c r="L31">
-        <v>160</v>
-      </c>
-      <c r="M31">
-        <v>164</v>
-      </c>
-      <c r="N31">
-        <v>163</v>
-      </c>
-      <c r="O31">
-        <v>166</v>
-      </c>
-      <c r="P31">
-        <v>164</v>
-      </c>
-      <c r="Q31">
-        <v>162</v>
-      </c>
-      <c r="S31">
-        <v>138</v>
-      </c>
-      <c r="T31">
-        <v>133</v>
-      </c>
-      <c r="U31">
-        <v>127</v>
-      </c>
-      <c r="V31" s="25">
-        <v>46231</v>
-      </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
-        <f t="shared" si="1"/>
-        <v>46232</v>
-      </c>
-      <c r="D32" s="4">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1">
-        <v>13</v>
-      </c>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="3">
-        <f t="shared" si="1"/>
-        <v>46233</v>
-      </c>
-      <c r="D33" s="4">
-        <v>0</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1">
-        <v>14</v>
-      </c>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
-        <f t="shared" si="1"/>
-        <v>46234</v>
-      </c>
-      <c r="D34" s="4">
-        <v>0</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1">
-        <v>12</v>
-      </c>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D36" s="4">
-        <f>SUM(D4:D34)</f>
-        <v>21</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/31</f>
-        <v>0.67741935483870963</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1">
-        <f>AVERAGE(G4:G34)</f>
-        <v>10.548387096774194</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
-        <v>0.52741935483870961</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="49" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="48" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="47" priority="3" operator="greaterThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -14040,19 +15461,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="30"/>
+      <c r="D3" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="31"/>
       <c r="F3" s="22"/>
-      <c r="G3" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
+      <c r="G3" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -14719,17 +16140,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="46" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="45" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="48" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="44" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="47" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14738,7 +16159,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -14755,19 +16176,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="30"/>
+      <c r="D3" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="31"/>
       <c r="F3" s="21"/>
-      <c r="G3" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
+      <c r="G3" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -15449,17 +16870,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="42" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="45" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="41" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="44" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15468,7 +16889,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -15485,19 +16906,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="30"/>
+      <c r="D3" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="31"/>
       <c r="F3" s="20"/>
-      <c r="G3" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
+      <c r="G3" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -16155,17 +17576,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="40" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="39" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="42" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="38" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="41" priority="3" operator="greaterThan">
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16174,7 +17595,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -16191,19 +17612,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="30"/>
+      <c r="D3" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="31"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
+      <c r="G3" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -16882,681 +18303,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="36" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="39" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="35" priority="3" operator="greaterThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:I33"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46295</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="30"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>46054</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>10</v>
-      </c>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>46055</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>12</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I31" si="0">G5/H5</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C31" si="1">C5+1</f>
-        <v>46056</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>14</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>46057</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>10</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>46058</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>12</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>46059</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>12</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>46060</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>8</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>46061</v>
-      </c>
-      <c r="D11" s="4">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>12</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>46062</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>12</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>46063</v>
-      </c>
-      <c r="D13" s="4">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>11</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>46064</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>10</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>46065</v>
-      </c>
-      <c r="D15" s="4">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>14</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>46066</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>12</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>46067</v>
-      </c>
-      <c r="D17" s="4">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>8</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>46068</v>
-      </c>
-      <c r="D18" s="4">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>12</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>46069</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>8</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>46070</v>
-      </c>
-      <c r="D20" s="4">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>8</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>46071</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>9</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>46072</v>
-      </c>
-      <c r="D22" s="4">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>12</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>46073</v>
-      </c>
-      <c r="D23" s="4">
-        <v>0</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>13</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>46074</v>
-      </c>
-      <c r="D24" s="4">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>10</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>46075</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>11</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>46076</v>
-      </c>
-      <c r="D26" s="4">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>13</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>46077</v>
-      </c>
-      <c r="D27" s="4">
-        <v>0</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>13</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>46078</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>10</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>46079</v>
-      </c>
-      <c r="D29" s="4">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>13</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>46080</v>
-      </c>
-      <c r="D30" s="4">
-        <v>0</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>8</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>46081</v>
-      </c>
-      <c r="D31" s="4">
-        <v>0</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>10</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="33" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D33" s="4">
-        <f>SUM(D4:D31)</f>
-        <v>4</v>
-      </c>
-      <c r="E33" s="5">
-        <f>D33/28</f>
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="F33" s="5"/>
-      <c r="G33" s="1">
-        <f>AVERAGE(G4:G31)</f>
-        <v>10.964285714285714</v>
-      </c>
-      <c r="H33" s="1"/>
-      <c r="I33" s="5">
-        <f>AVERAGE(I4:I31)</f>
-        <v>0.54821428571428577</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C31">
-    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D31">
-    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G31">
-    <cfRule type="cellIs" dxfId="32" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1663,11 +1663,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1706,21 +1706,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2662,23 +2662,23 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="31"/>
+      <c r="D3" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="32"/>
       <c r="F3" s="29"/>
       <c r="G3" s="2" t="s">
         <v>37</v>
       </c>
       <c r="H3" s="29"/>
-      <c r="I3" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
+      <c r="I3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
       <c r="M3" s="1" t="s">
         <v>32</v>
       </c>
@@ -3363,19 +3363,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="31"/>
+      <c r="D3" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="32"/>
       <c r="F3" s="18"/>
-      <c r="G3" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
+      <c r="G3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -3991,17 +3991,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C31">
-    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D31">
-    <cfRule type="cellIs" dxfId="36" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G31">
-    <cfRule type="cellIs" dxfId="35" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="32" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4027,19 +4027,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="31"/>
+      <c r="D3" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="32"/>
       <c r="F3" s="17"/>
-      <c r="G3" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
+      <c r="G3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -4707,733 +4707,6 @@
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
         <v>0.54838709677419339</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="32" priority="3" operator="greaterThan">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:I36"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46296</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="31"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>45992</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>45993</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>10</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>45994</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>8</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>45995</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>8</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>45996</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>10</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>45997</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>10</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>45998</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>10</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>45999</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>11</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>46000</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>10</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>46001</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>11</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>46002</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>12</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>46003</v>
-      </c>
-      <c r="D15" s="4">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>10</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>46004</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>8</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>46005</v>
-      </c>
-      <c r="D17" s="4">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>10</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>46006</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>10</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>46007</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>10</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>46008</v>
-      </c>
-      <c r="D20" s="4">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>10</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>46009</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>10</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>46010</v>
-      </c>
-      <c r="D22" s="4">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>10</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>46011</v>
-      </c>
-      <c r="D23" s="4">
-        <v>2</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>11</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>46012</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>8</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>46013</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>12</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>46014</v>
-      </c>
-      <c r="D26" s="4">
-        <v>1</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>11</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>46015</v>
-      </c>
-      <c r="D27" s="4">
-        <v>0</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>11</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>46016</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>8</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>46017</v>
-      </c>
-      <c r="D29" s="4">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>9</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>46018</v>
-      </c>
-      <c r="D30" s="4">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>6</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>46019</v>
-      </c>
-      <c r="D31" s="4">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>10</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
-        <f t="shared" si="1"/>
-        <v>46020</v>
-      </c>
-      <c r="D32" s="4">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1">
-        <v>12</v>
-      </c>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="3">
-        <f t="shared" si="1"/>
-        <v>46021</v>
-      </c>
-      <c r="D33" s="4">
-        <v>0</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1">
-        <v>12</v>
-      </c>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
-        <f t="shared" si="1"/>
-        <v>46022</v>
-      </c>
-      <c r="D34" s="4">
-        <v>0</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1">
-        <v>8</v>
-      </c>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D36" s="4">
-        <f>SUM(D4:D34)</f>
-        <v>7</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/31</f>
-        <v>0.22580645161290322</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1">
-        <f>AVERAGE(G4:G34)</f>
-        <v>9.935483870967742</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
-        <v>0.49677419354838714</v>
       </c>
     </row>
   </sheetData>
@@ -5462,6 +4735,733 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:I36"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46297</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="32"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>45992</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>45993</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>10</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>45994</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>8</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>45995</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>8</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>45996</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>45997</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>45998</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>45999</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>11</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>46000</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>46001</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>11</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>46002</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>12</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>46003</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>10</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>46004</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>8</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>46005</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>10</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>46006</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>10</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>46007</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>46008</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>10</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>46009</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>10</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>46010</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>10</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>46011</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>11</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>46012</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>8</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>46013</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>12</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>46014</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>11</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>46015</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>11</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>46016</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>8</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>46017</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>9</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>46018</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>6</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>46019</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>46020</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1">
+        <v>12</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>46021</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>12</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>46022</v>
+      </c>
+      <c r="D34" s="4">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1">
+        <v>8</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>7</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0.22580645161290322</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>9.935483870967742</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0.49677419354838714</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="26" priority="3" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I35"/>
@@ -5479,19 +5479,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="31"/>
+      <c r="D3" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="32"/>
       <c r="F3" s="15"/>
-      <c r="G3" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
+      <c r="G3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -6149,17 +6149,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="26" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="23" priority="3" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6185,19 +6185,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="31"/>
+      <c r="D3" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="32"/>
       <c r="F3" s="14"/>
-      <c r="G3" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
+      <c r="G3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -6882,17 +6882,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="23" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6918,19 +6918,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="31"/>
+      <c r="D3" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="32"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
+      <c r="G3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -7597,17 +7597,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="20" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="3" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7633,19 +7633,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="31"/>
+      <c r="D3" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="32"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
+      <c r="G3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -8324,760 +8324,6 @@
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
         <v>0.44838709677419353</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="18" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="17" priority="3" operator="greaterThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:J40"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="8.25" customWidth="1"/>
-    <col min="6" max="6" width="5.25" customWidth="1"/>
-    <col min="7" max="9" width="8.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46296</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="31"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>45839</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>45840</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>8</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>45841</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>10</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>45842</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>9</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>45843</v>
-      </c>
-      <c r="D8" s="4">
-        <v>2</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>12</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>45844</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>10</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="J9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>45845</v>
-      </c>
-      <c r="D10" s="4">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>9</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>45846</v>
-      </c>
-      <c r="D11" s="4">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>9</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>45847</v>
-      </c>
-      <c r="D12" s="4">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>11</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>45848</v>
-      </c>
-      <c r="D13" s="4">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>14</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-      <c r="J13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>45849</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>12</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>45850</v>
-      </c>
-      <c r="D15" s="4">
-        <v>2</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>11</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>45851</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>10</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>45852</v>
-      </c>
-      <c r="D17" s="4">
-        <v>1</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>9</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>45853</v>
-      </c>
-      <c r="D18" s="4">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>16</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="J18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>45854</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>8</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>45855</v>
-      </c>
-      <c r="D20" s="4">
-        <v>1</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>13</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>45856</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>9</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>45857</v>
-      </c>
-      <c r="D22" s="4">
-        <v>2</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>9</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>45858</v>
-      </c>
-      <c r="D23" s="4">
-        <v>2</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>8</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-      <c r="J23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>45859</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>9</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>45860</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>9</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>45861</v>
-      </c>
-      <c r="D26" s="4">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>11</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>45862</v>
-      </c>
-      <c r="D27" s="4">
-        <v>1</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>8</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>45863</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>8</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>45864</v>
-      </c>
-      <c r="D29" s="4">
-        <v>1</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>10</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>45865</v>
-      </c>
-      <c r="D30" s="4">
-        <v>0</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>10</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>45866</v>
-      </c>
-      <c r="D31" s="4">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>10</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
-        <f t="shared" si="1"/>
-        <v>45867</v>
-      </c>
-      <c r="D32" s="4">
-        <v>2</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1">
-        <v>10</v>
-      </c>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="3">
-        <f t="shared" si="1"/>
-        <v>45868</v>
-      </c>
-      <c r="D33" s="4">
-        <v>1</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1">
-        <v>8</v>
-      </c>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
-        <f t="shared" si="1"/>
-        <v>45869</v>
-      </c>
-      <c r="D34" s="4">
-        <v>1</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1">
-        <v>11</v>
-      </c>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D36" s="4">
-        <f>SUM(D4:D34)</f>
-        <v>27</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/31</f>
-        <v>0.87096774193548387</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1">
-        <f>AVERAGE(G4:G34)</f>
-        <v>10.096774193548388</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
-        <v>0.50483870967741939</v>
-      </c>
-    </row>
-    <row r="39" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="E39" s="8"/>
-    </row>
-    <row r="40" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="E40" s="8">
-        <f>SUM(D4:D34)/31</f>
-        <v>0.87096774193548387</v>
       </c>
     </row>
   </sheetData>
@@ -9106,6 +8352,760 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:J40"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.25" customWidth="1"/>
+    <col min="6" max="6" width="5.25" customWidth="1"/>
+    <col min="7" max="9" width="8.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46297</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="32"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>45839</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>45840</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>8</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>45841</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>45842</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>9</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>45843</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>12</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>45844</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="J9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>45845</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>9</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>45846</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>9</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>45847</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>11</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>45848</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>14</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+      <c r="J13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>45849</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>12</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>45850</v>
+      </c>
+      <c r="D15" s="4">
+        <v>2</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>11</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>45851</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>10</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>45852</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>9</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>45853</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>16</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="J18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>45854</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>8</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>45855</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>13</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>45856</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>9</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>45857</v>
+      </c>
+      <c r="D22" s="4">
+        <v>2</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>9</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>45858</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>8</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="J23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>45859</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>9</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>45860</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>9</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>45861</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>11</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>45862</v>
+      </c>
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>8</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>45863</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>8</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>45864</v>
+      </c>
+      <c r="D29" s="4">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>10</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>45865</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>10</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>45866</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>45867</v>
+      </c>
+      <c r="D32" s="4">
+        <v>2</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1">
+        <v>10</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>45868</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>8</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>45869</v>
+      </c>
+      <c r="D34" s="4">
+        <v>1</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1">
+        <v>11</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>27</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0.87096774193548387</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>10.096774193548388</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0.50483870967741939</v>
+      </c>
+    </row>
+    <row r="39" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="E39" s="8"/>
+    </row>
+    <row r="40" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="E40" s="8">
+        <f>SUM(D4:D34)/31</f>
+        <v>0.87096774193548387</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J39"/>
@@ -9123,19 +9123,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="31"/>
+      <c r="D3" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="32"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
+      <c r="G3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -9814,17 +9814,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9850,19 +9850,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="31"/>
+      <c r="D3" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="32"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
+      <c r="G3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -10559,17 +10559,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10605,23 +10605,23 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="31"/>
+      <c r="D3" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="32"/>
       <c r="F3" s="30"/>
       <c r="G3" s="30" t="s">
         <v>37</v>
       </c>
       <c r="H3" s="30"/>
-      <c r="I3" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
+      <c r="I3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
       <c r="M3" s="1" t="s">
         <v>32</v>
       </c>
@@ -10658,18 +10658,22 @@
       <c r="C4" s="3">
         <v>46296</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="32"/>
+      <c r="G4" s="31"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="1"/>
+      <c r="I4" s="1">
+        <v>10</v>
+      </c>
       <c r="J4" s="1">
         <v>20</v>
       </c>
       <c r="K4" s="5">
         <f>I4/J4</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="2:23" x14ac:dyDescent="0.3">
@@ -10680,7 +10684,7 @@
       <c r="D5" s="4"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="G5" s="31"/>
       <c r="H5" s="3"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1">
@@ -11245,23 +11249,23 @@
     <row r="36" spans="3:11" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0</v>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
-      <c r="I36" s="1" t="e">
+      <c r="I36" s="1">
         <f>AVERAGE(I4:I34)</f>
-        <v>#DIV/0!</v>
+        <v>10</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="5">
         <f>AVERAGE(K4:K34)</f>
-        <v>0</v>
+        <v>1.6129032258064516E-2</v>
       </c>
     </row>
   </sheetData>
@@ -11271,21 +11275,22 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="57" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4:I34">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="56" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11306,19 +11311,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="31"/>
+      <c r="D3" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="32"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
+      <c r="G3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -11947,17 +11952,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
       <formula>12</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11977,16 +11982,16 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="1"/>
-      <c r="C2" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="31"/>
+      <c r="C2" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="32"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
+      <c r="F2" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="3">
@@ -12635,12 +12640,12 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3:C33">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F33">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
       <formula>14</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12670,19 +12675,19 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="31"/>
+      <c r="D3" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="32"/>
       <c r="F3" s="28"/>
-      <c r="G3" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
+      <c r="G3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
       <c r="K3" s="1" t="s">
         <v>32</v>
       </c>
@@ -13371,17 +13376,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="58" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="57" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="54" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="56" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="53" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13415,19 +13420,19 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="31"/>
+      <c r="D3" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="32"/>
       <c r="F3" s="27"/>
-      <c r="G3" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
+      <c r="G3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
       <c r="K3" s="1" t="s">
         <v>32</v>
       </c>
@@ -14305,17 +14310,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="55" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="54" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="51" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="53" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="50" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14348,19 +14353,19 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="31"/>
+      <c r="D3" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="32"/>
       <c r="F3" s="24"/>
-      <c r="G3" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
+      <c r="G3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
       <c r="K3" s="1" t="s">
         <v>32</v>
       </c>
@@ -15424,17 +15429,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="52" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="51" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="48" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="50" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="47" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15461,19 +15466,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="31"/>
+      <c r="D3" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="32"/>
       <c r="F3" s="22"/>
-      <c r="G3" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
+      <c r="G3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -16140,17 +16145,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="49" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="48" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="45" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="47" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="44" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16176,19 +16181,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="31"/>
+      <c r="D3" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="32"/>
       <c r="F3" s="21"/>
-      <c r="G3" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
+      <c r="G3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -16870,17 +16875,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="46" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="45" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="42" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="44" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="41" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16906,19 +16911,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="31"/>
+      <c r="D3" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="32"/>
       <c r="F3" s="20"/>
-      <c r="G3" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
+      <c r="G3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -17576,17 +17581,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="42" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="39" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="41" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="3" operator="greaterThan">
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17612,19 +17617,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="31"/>
+      <c r="D3" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="32"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
+      <c r="G3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -18303,17 +18308,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="40" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="39" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="36" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="38" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="35" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1520,7 +1520,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1536,6 +1536,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1569,7 +1575,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1664,6 +1670,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2662,23 +2674,23 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="32"/>
+      <c r="D3" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="34"/>
       <c r="F3" s="29"/>
       <c r="G3" s="2" t="s">
         <v>37</v>
       </c>
       <c r="H3" s="29"/>
-      <c r="I3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
+      <c r="I3" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
       <c r="M3" s="1" t="s">
         <v>32</v>
       </c>
@@ -3363,19 +3375,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="32"/>
+      <c r="D3" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="34"/>
       <c r="F3" s="18"/>
-      <c r="G3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="G3" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -4027,19 +4039,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="32"/>
+      <c r="D3" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="34"/>
       <c r="F3" s="17"/>
-      <c r="G3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="G3" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -4752,19 +4764,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="32"/>
+      <c r="D3" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="34"/>
       <c r="F3" s="16"/>
-      <c r="G3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="G3" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -5479,19 +5491,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="32"/>
+      <c r="D3" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="34"/>
       <c r="F3" s="15"/>
-      <c r="G3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="G3" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -6185,19 +6197,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="32"/>
+      <c r="D3" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="34"/>
       <c r="F3" s="14"/>
-      <c r="G3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="G3" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -6918,19 +6930,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="32"/>
+      <c r="D3" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="34"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="G3" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -7633,19 +7645,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="32"/>
+      <c r="D3" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="34"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="G3" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -8372,19 +8384,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="32"/>
+      <c r="D3" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="34"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="G3" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -9123,19 +9135,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="32"/>
+      <c r="D3" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="34"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="G3" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -9850,19 +9862,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="32"/>
+      <c r="D3" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="34"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="G3" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -10581,7 +10593,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:W36"/>
+  <dimension ref="B2:X36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
@@ -10589,39 +10601,39 @@
     <col min="6" max="6" width="0.75" customWidth="1"/>
     <col min="7" max="7" width="11.875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="0.75" customWidth="1"/>
-    <col min="13" max="13" width="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.25" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.5" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="5" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="0.875" customWidth="1"/>
-    <col min="21" max="23" width="4" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="32"/>
+      <c r="D3" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="34"/>
       <c r="F3" s="30"/>
       <c r="G3" s="30" t="s">
         <v>37</v>
       </c>
       <c r="H3" s="30"/>
-      <c r="I3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
+      <c r="I3" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
       <c r="M3" s="1" t="s">
         <v>32</v>
       </c>
@@ -10654,7 +10666,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:24" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
         <v>46296</v>
       </c>
@@ -10676,83 +10688,132 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:24" x14ac:dyDescent="0.3">
       <c r="C5" s="3">
         <f>C4+1</f>
         <v>46297</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="31"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="1"/>
+      <c r="I5" s="1">
+        <v>14</v>
+      </c>
       <c r="J5" s="1">
         <v>20</v>
       </c>
       <c r="K5" s="5">
         <f t="shared" ref="K5:K34" si="0">I5/J5</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="2:23" x14ac:dyDescent="0.3">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:24" x14ac:dyDescent="0.3">
       <c r="C6" s="3">
         <f t="shared" ref="C6:C34" si="1">C5+1</f>
         <v>46298</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="G6" s="32"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="1"/>
+      <c r="I6" s="1">
+        <v>11</v>
+      </c>
       <c r="J6" s="1">
         <v>20</v>
       </c>
       <c r="K6" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:23" x14ac:dyDescent="0.3">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="2:24" x14ac:dyDescent="0.3">
       <c r="C7" s="3">
         <f t="shared" si="1"/>
         <v>46299</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+      <c r="G7" s="32"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="1"/>
+      <c r="I7" s="1">
+        <v>10</v>
+      </c>
       <c r="J7" s="1">
         <v>20</v>
       </c>
       <c r="K7" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:23" x14ac:dyDescent="0.3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:24" x14ac:dyDescent="0.3">
       <c r="C8" s="3">
         <f t="shared" si="1"/>
         <v>46300</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="4">
+        <v>1</v>
+      </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="1"/>
+      <c r="I8" s="1">
+        <v>11</v>
+      </c>
       <c r="J8" s="1">
         <v>20</v>
       </c>
       <c r="K8" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:23" x14ac:dyDescent="0.3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="M8">
+        <v>150</v>
+      </c>
+      <c r="N8">
+        <v>160</v>
+      </c>
+      <c r="O8">
+        <v>166</v>
+      </c>
+      <c r="P8">
+        <v>170</v>
+      </c>
+      <c r="Q8">
+        <v>171</v>
+      </c>
+      <c r="R8">
+        <v>176</v>
+      </c>
+      <c r="S8">
+        <v>178</v>
+      </c>
+      <c r="U8">
+        <v>150</v>
+      </c>
+      <c r="V8">
+        <v>142</v>
+      </c>
+      <c r="W8">
+        <v>139</v>
+      </c>
+      <c r="X8" s="25">
+        <v>46300</v>
+      </c>
+    </row>
+    <row r="9" spans="2:24" x14ac:dyDescent="0.3">
       <c r="C9" s="3">
         <f t="shared" si="1"/>
         <v>46301</v>
@@ -10771,7 +10832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:24" x14ac:dyDescent="0.3">
       <c r="C10" s="3">
         <f t="shared" si="1"/>
         <v>46302</v>
@@ -10790,7 +10851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:24" x14ac:dyDescent="0.3">
       <c r="C11" s="3">
         <f t="shared" si="1"/>
         <v>46303</v>
@@ -10809,7 +10870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:24" x14ac:dyDescent="0.3">
       <c r="C12" s="3">
         <f t="shared" si="1"/>
         <v>46304</v>
@@ -10828,7 +10889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:24" x14ac:dyDescent="0.3">
       <c r="C13" s="3">
         <f t="shared" si="1"/>
         <v>46305</v>
@@ -10847,7 +10908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:24" x14ac:dyDescent="0.3">
       <c r="C14" s="3">
         <f t="shared" si="1"/>
         <v>46306</v>
@@ -10866,7 +10927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:24" x14ac:dyDescent="0.3">
       <c r="C15" s="3">
         <f t="shared" si="1"/>
         <v>46307</v>
@@ -10885,7 +10946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:24" x14ac:dyDescent="0.3">
       <c r="C16" s="3">
         <f t="shared" si="1"/>
         <v>46308</v>
@@ -11249,23 +11310,23 @@
     <row r="36" spans="3:11" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>3.2258064516129031E-2</v>
+        <v>9.6774193548387094E-2</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="1">
         <f>AVERAGE(I4:I34)</f>
-        <v>10</v>
+        <v>11.2</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="5">
         <f>AVERAGE(K4:K34)</f>
-        <v>1.6129032258064516E-2</v>
+        <v>9.0322580645161285E-2</v>
       </c>
     </row>
   </sheetData>
@@ -11311,19 +11372,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="32"/>
+      <c r="D3" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="34"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="G3" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -11982,16 +12043,16 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="1"/>
-      <c r="C2" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="32"/>
+      <c r="C2" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="34"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="F2" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="3">
@@ -12675,19 +12736,19 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="32"/>
+      <c r="D3" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="34"/>
       <c r="F3" s="28"/>
-      <c r="G3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="G3" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
       <c r="K3" s="1" t="s">
         <v>32</v>
       </c>
@@ -13420,19 +13481,19 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="32"/>
+      <c r="D3" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="34"/>
       <c r="F3" s="27"/>
-      <c r="G3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="G3" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
       <c r="K3" s="1" t="s">
         <v>32</v>
       </c>
@@ -14353,19 +14414,19 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="32"/>
+      <c r="D3" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="34"/>
       <c r="F3" s="24"/>
-      <c r="G3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="G3" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
       <c r="K3" s="1" t="s">
         <v>32</v>
       </c>
@@ -15466,19 +15527,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="32"/>
+      <c r="D3" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="34"/>
       <c r="F3" s="22"/>
-      <c r="G3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="G3" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -16181,19 +16242,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="32"/>
+      <c r="D3" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="34"/>
       <c r="F3" s="21"/>
-      <c r="G3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="G3" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -16911,19 +16972,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="32"/>
+      <c r="D3" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="34"/>
       <c r="F3" s="20"/>
-      <c r="G3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="G3" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -17617,19 +17678,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="32"/>
+      <c r="D3" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="34"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="G3" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1520,7 +1520,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1542,6 +1542,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1575,7 +1581,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1680,6 +1686,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2674,7 +2683,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="34" t="s">
@@ -3375,7 +3384,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="34" t="s">
@@ -4039,7 +4048,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="34" t="s">
@@ -4764,7 +4773,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="34" t="s">
@@ -5491,7 +5500,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="34" t="s">
@@ -6197,7 +6206,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="34" t="s">
@@ -6930,7 +6939,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="34" t="s">
@@ -7645,7 +7654,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="34" t="s">
@@ -8384,7 +8393,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="34" t="s">
@@ -9135,7 +9144,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="34" t="s">
@@ -9862,7 +9871,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="34" t="s">
@@ -10617,7 +10626,7 @@
     <row r="3" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="34" t="s">
@@ -10818,18 +10827,22 @@
         <f t="shared" si="1"/>
         <v>46301</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
+      <c r="G9" s="35"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="1"/>
+      <c r="I9" s="1">
+        <v>11</v>
+      </c>
       <c r="J9" s="1">
         <v>20</v>
       </c>
       <c r="K9" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="10" spans="2:24" x14ac:dyDescent="0.3">
@@ -10840,7 +10853,7 @@
       <c r="D10" s="4"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+      <c r="G10" s="31"/>
       <c r="H10" s="3"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1">
@@ -11321,12 +11334,12 @@
       <c r="H36" s="5"/>
       <c r="I36" s="1">
         <f>AVERAGE(I4:I34)</f>
-        <v>11.2</v>
+        <v>11.166666666666666</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="5">
         <f>AVERAGE(K4:K34)</f>
-        <v>9.0322580645161285E-2</v>
+        <v>0.10806451612903224</v>
       </c>
     </row>
   </sheetData>
@@ -11372,7 +11385,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="34" t="s">
@@ -12736,7 +12749,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="34" t="s">
@@ -13481,7 +13494,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="34" t="s">
@@ -14414,7 +14427,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="34" t="s">
@@ -15527,7 +15540,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="34" t="s">
@@ -16242,7 +16255,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="34" t="s">
@@ -16972,7 +16985,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="34" t="s">
@@ -17678,7 +17691,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="34" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1684,11 +1684,11 @@
     <xf numFmtId="176" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2683,23 +2683,23 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="34"/>
+      <c r="D3" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="35"/>
       <c r="F3" s="29"/>
       <c r="G3" s="2" t="s">
         <v>37</v>
       </c>
       <c r="H3" s="29"/>
-      <c r="I3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
+      <c r="I3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
       <c r="M3" s="1" t="s">
         <v>32</v>
       </c>
@@ -3384,19 +3384,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="34"/>
+      <c r="D3" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="35"/>
       <c r="F3" s="18"/>
-      <c r="G3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
+      <c r="G3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -4048,19 +4048,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="34"/>
+      <c r="D3" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="35"/>
       <c r="F3" s="17"/>
-      <c r="G3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
+      <c r="G3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -4773,19 +4773,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="34"/>
+      <c r="D3" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="35"/>
       <c r="F3" s="16"/>
-      <c r="G3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
+      <c r="G3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -5500,19 +5500,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="34"/>
+      <c r="D3" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="35"/>
       <c r="F3" s="15"/>
-      <c r="G3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
+      <c r="G3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -6206,19 +6206,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="34"/>
+      <c r="D3" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="35"/>
       <c r="F3" s="14"/>
-      <c r="G3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
+      <c r="G3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -6939,19 +6939,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="34"/>
+      <c r="D3" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="35"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
+      <c r="G3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -7654,19 +7654,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="34"/>
+      <c r="D3" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="35"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
+      <c r="G3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -8393,19 +8393,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="34"/>
+      <c r="D3" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="35"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
+      <c r="G3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -9144,19 +9144,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="34"/>
+      <c r="D3" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="35"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
+      <c r="G3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -9871,19 +9871,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="34"/>
+      <c r="D3" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="35"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
+      <c r="G3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -10626,23 +10626,23 @@
     <row r="3" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="34"/>
+      <c r="D3" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="35"/>
       <c r="F3" s="30"/>
       <c r="G3" s="30" t="s">
         <v>37</v>
       </c>
       <c r="H3" s="30"/>
-      <c r="I3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
+      <c r="I3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
       <c r="M3" s="1" t="s">
         <v>32</v>
       </c>
@@ -10832,7 +10832,7 @@
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="35"/>
+      <c r="G9" s="34"/>
       <c r="H9" s="3"/>
       <c r="I9" s="1">
         <v>11</v>
@@ -10850,18 +10850,22 @@
         <f t="shared" si="1"/>
         <v>46302</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="31"/>
       <c r="H10" s="3"/>
-      <c r="I10" s="1"/>
+      <c r="I10" s="1">
+        <v>11</v>
+      </c>
       <c r="J10" s="1">
         <v>20</v>
       </c>
       <c r="K10" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="11" spans="2:24" x14ac:dyDescent="0.3">
@@ -10872,7 +10876,7 @@
       <c r="D11" s="4"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
+      <c r="G11" s="31"/>
       <c r="H11" s="3"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1">
@@ -11334,12 +11338,12 @@
       <c r="H36" s="5"/>
       <c r="I36" s="1">
         <f>AVERAGE(I4:I34)</f>
-        <v>11.166666666666666</v>
+        <v>11.142857142857142</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="5">
         <f>AVERAGE(K4:K34)</f>
-        <v>0.10806451612903224</v>
+        <v>0.12580645161290321</v>
       </c>
     </row>
   </sheetData>
@@ -11385,19 +11389,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="34"/>
+      <c r="D3" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="35"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
+      <c r="G3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -12056,16 +12060,16 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="1"/>
-      <c r="C2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="34"/>
+      <c r="C2" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="35"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
+      <c r="F2" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="3">
@@ -12749,19 +12753,19 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="34"/>
+      <c r="D3" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="35"/>
       <c r="F3" s="28"/>
-      <c r="G3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
+      <c r="G3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
       <c r="K3" s="1" t="s">
         <v>32</v>
       </c>
@@ -13494,19 +13498,19 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="34"/>
+      <c r="D3" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="35"/>
       <c r="F3" s="27"/>
-      <c r="G3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
+      <c r="G3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
       <c r="K3" s="1" t="s">
         <v>32</v>
       </c>
@@ -14427,19 +14431,19 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="34"/>
+      <c r="D3" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="35"/>
       <c r="F3" s="24"/>
-      <c r="G3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
+      <c r="G3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
       <c r="K3" s="1" t="s">
         <v>32</v>
       </c>
@@ -15540,19 +15544,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="34"/>
+      <c r="D3" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="35"/>
       <c r="F3" s="22"/>
-      <c r="G3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
+      <c r="G3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -16255,19 +16259,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="34"/>
+      <c r="D3" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="35"/>
       <c r="F3" s="21"/>
-      <c r="G3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
+      <c r="G3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -16985,19 +16989,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="34"/>
+      <c r="D3" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="35"/>
       <c r="F3" s="20"/>
-      <c r="G3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
+      <c r="G3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -17691,19 +17695,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="34"/>
+      <c r="D3" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="35"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
+      <c r="G3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2683,7 +2683,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -3384,7 +3384,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -4048,7 +4048,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -4773,7 +4773,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -5500,7 +5500,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -6206,7 +6206,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -6939,7 +6939,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -7654,7 +7654,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -8393,7 +8393,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -9144,7 +9144,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -9871,7 +9871,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -10626,7 +10626,7 @@
     <row r="3" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -10873,18 +10873,22 @@
         <f t="shared" si="1"/>
         <v>46303</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="31"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="1"/>
+      <c r="I11" s="1">
+        <v>11</v>
+      </c>
       <c r="J11" s="1">
         <v>20</v>
       </c>
       <c r="K11" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="12" spans="2:24" x14ac:dyDescent="0.3">
@@ -10892,18 +10896,22 @@
         <f t="shared" si="1"/>
         <v>46304</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
+      <c r="G12" s="31"/>
       <c r="H12" s="3"/>
-      <c r="I12" s="1"/>
+      <c r="I12" s="1">
+        <v>9</v>
+      </c>
       <c r="J12" s="1">
         <v>20</v>
       </c>
       <c r="K12" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="13" spans="2:24" x14ac:dyDescent="0.3">
@@ -10911,18 +10919,22 @@
         <f t="shared" si="1"/>
         <v>46305</v>
       </c>
-      <c r="D13" s="4"/>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
+      <c r="G13" s="32"/>
       <c r="H13" s="3"/>
-      <c r="I13" s="1"/>
+      <c r="I13" s="1">
+        <v>11</v>
+      </c>
       <c r="J13" s="1">
         <v>20</v>
       </c>
       <c r="K13" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="14" spans="2:24" x14ac:dyDescent="0.3">
@@ -10930,18 +10942,22 @@
         <f t="shared" si="1"/>
         <v>46306</v>
       </c>
-      <c r="D14" s="4"/>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
+      <c r="G14" s="31"/>
       <c r="H14" s="3"/>
-      <c r="I14" s="1"/>
+      <c r="I14" s="1">
+        <v>12</v>
+      </c>
       <c r="J14" s="1">
         <v>20</v>
       </c>
       <c r="K14" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="15" spans="2:24" x14ac:dyDescent="0.3">
@@ -10952,7 +10968,7 @@
       <c r="D15" s="4"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
+      <c r="G15" s="31"/>
       <c r="H15" s="3"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1">
@@ -11327,23 +11343,23 @@
     <row r="36" spans="3:11" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>9.6774193548387094E-2</v>
+        <v>0.16129032258064516</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="1">
         <f>AVERAGE(I4:I34)</f>
-        <v>11.142857142857142</v>
+        <v>11</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="5">
         <f>AVERAGE(K4:K34)</f>
-        <v>0.12580645161290321</v>
+        <v>0.19516129032258062</v>
       </c>
     </row>
   </sheetData>
@@ -11389,7 +11405,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -12753,7 +12769,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -13498,7 +13514,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -14431,7 +14447,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -15544,7 +15560,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -16259,7 +16275,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -16989,7 +17005,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -17695,7 +17711,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2683,7 +2683,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -3384,7 +3384,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -4048,7 +4048,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -4773,7 +4773,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -5500,7 +5500,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -6206,7 +6206,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -6939,7 +6939,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -7654,7 +7654,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -8393,7 +8393,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -9144,7 +9144,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -9871,7 +9871,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -10626,7 +10626,7 @@
     <row r="3" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -10965,18 +10965,22 @@
         <f t="shared" si="1"/>
         <v>46307</v>
       </c>
-      <c r="D15" s="4"/>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="31"/>
       <c r="H15" s="3"/>
-      <c r="I15" s="1"/>
+      <c r="I15" s="1">
+        <v>15</v>
+      </c>
       <c r="J15" s="1">
         <v>20</v>
       </c>
       <c r="K15" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="16" spans="2:24" x14ac:dyDescent="0.3">
@@ -10987,7 +10991,7 @@
       <c r="D16" s="4"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
+      <c r="G16" s="31"/>
       <c r="H16" s="3"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1">
@@ -11343,23 +11347,23 @@
     <row r="36" spans="3:11" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.16129032258064516</v>
+        <v>0.19354838709677419</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="1">
         <f>AVERAGE(I4:I34)</f>
-        <v>11</v>
+        <v>11.333333333333334</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="5">
         <f>AVERAGE(K4:K34)</f>
-        <v>0.19516129032258062</v>
+        <v>0.2193548387096774</v>
       </c>
     </row>
   </sheetData>
@@ -11405,7 +11409,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -12769,7 +12773,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -13514,7 +13518,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -14447,7 +14451,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -15560,7 +15564,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -16275,7 +16279,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -17005,7 +17009,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -17711,7 +17715,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2683,7 +2683,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -3384,7 +3384,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -4048,7 +4048,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -4773,7 +4773,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -5500,7 +5500,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -6206,7 +6206,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -6939,7 +6939,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -7654,7 +7654,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -8393,7 +8393,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -9144,7 +9144,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -9871,7 +9871,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -10626,7 +10626,7 @@
     <row r="3" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -10988,18 +10988,22 @@
         <f t="shared" si="1"/>
         <v>46308</v>
       </c>
-      <c r="D16" s="4"/>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="31"/>
       <c r="H16" s="3"/>
-      <c r="I16" s="1"/>
+      <c r="I16" s="1">
+        <v>11</v>
+      </c>
       <c r="J16" s="1">
         <v>20</v>
       </c>
       <c r="K16" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="17" spans="3:11" x14ac:dyDescent="0.3">
@@ -11010,7 +11014,7 @@
       <c r="D17" s="4"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
+      <c r="G17" s="31"/>
       <c r="H17" s="3"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1">
@@ -11347,23 +11351,23 @@
     <row r="36" spans="3:11" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.19354838709677419</v>
+        <v>0.22580645161290322</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="1">
         <f>AVERAGE(I4:I34)</f>
-        <v>11.333333333333334</v>
+        <v>11.307692307692308</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="5">
         <f>AVERAGE(K4:K34)</f>
-        <v>0.2193548387096774</v>
+        <v>0.23709677419354835</v>
       </c>
     </row>
   </sheetData>
@@ -11409,7 +11413,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -12773,7 +12777,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -13518,7 +13522,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -14451,7 +14455,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -15564,7 +15568,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -16279,7 +16283,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -17009,7 +17013,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -17715,7 +17719,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2683,7 +2683,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -3384,7 +3384,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -4048,7 +4048,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -4773,7 +4773,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -5500,7 +5500,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -6206,7 +6206,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -6939,7 +6939,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -7654,7 +7654,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -8393,7 +8393,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -9144,7 +9144,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -9871,7 +9871,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -10626,7 +10626,7 @@
     <row r="3" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -11011,18 +11011,22 @@
         <f t="shared" si="1"/>
         <v>46309</v>
       </c>
-      <c r="D17" s="4"/>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="31"/>
       <c r="H17" s="3"/>
-      <c r="I17" s="1"/>
+      <c r="I17" s="1">
+        <v>12</v>
+      </c>
       <c r="J17" s="1">
         <v>20</v>
       </c>
       <c r="K17" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="18" spans="3:11" x14ac:dyDescent="0.3">
@@ -11033,7 +11037,7 @@
       <c r="D18" s="4"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
+      <c r="G18" s="31"/>
       <c r="H18" s="3"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1">
@@ -11351,23 +11355,23 @@
     <row r="36" spans="3:11" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.22580645161290322</v>
+        <v>0.25806451612903225</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="1">
         <f>AVERAGE(I4:I34)</f>
-        <v>11.307692307692308</v>
+        <v>11.357142857142858</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="5">
         <f>AVERAGE(K4:K34)</f>
-        <v>0.23709677419354835</v>
+        <v>0.25645161290322577</v>
       </c>
     </row>
   </sheetData>
@@ -11413,7 +11417,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -12777,7 +12781,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -13522,7 +13526,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -14455,7 +14459,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -15568,7 +15572,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -16283,7 +16287,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -17013,7 +17017,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -17719,7 +17723,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2683,7 +2683,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -3384,7 +3384,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -4048,7 +4048,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -4773,7 +4773,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -5500,7 +5500,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -6206,7 +6206,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -6939,7 +6939,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -7654,7 +7654,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -8393,7 +8393,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -9144,7 +9144,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -9871,7 +9871,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -10626,7 +10626,7 @@
     <row r="3" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -11034,18 +11034,22 @@
         <f t="shared" si="1"/>
         <v>46310</v>
       </c>
-      <c r="D18" s="4"/>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="31"/>
       <c r="H18" s="3"/>
-      <c r="I18" s="1"/>
+      <c r="I18" s="1">
+        <v>12</v>
+      </c>
       <c r="J18" s="1">
         <v>20</v>
       </c>
       <c r="K18" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="19" spans="3:11" x14ac:dyDescent="0.3">
@@ -11056,7 +11060,7 @@
       <c r="D19" s="4"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
+      <c r="G19" s="31"/>
       <c r="H19" s="3"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1">
@@ -11366,12 +11370,12 @@
       <c r="H36" s="5"/>
       <c r="I36" s="1">
         <f>AVERAGE(I4:I34)</f>
-        <v>11.357142857142858</v>
+        <v>11.4</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="5">
         <f>AVERAGE(K4:K34)</f>
-        <v>0.25645161290322577</v>
+        <v>0.27580645161290318</v>
       </c>
     </row>
   </sheetData>
@@ -11417,7 +11421,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -12781,7 +12785,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -13526,7 +13530,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -14459,7 +14463,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -15572,7 +15576,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -16287,7 +16291,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -17017,7 +17021,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -17723,7 +17727,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2683,7 +2683,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -3384,7 +3384,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -4048,7 +4048,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -4773,7 +4773,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -5500,7 +5500,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -6206,7 +6206,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -6939,7 +6939,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -7654,7 +7654,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -8393,7 +8393,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -9144,7 +9144,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -9871,7 +9871,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -10626,7 +10626,7 @@
     <row r="3" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -11057,18 +11057,22 @@
         <f t="shared" si="1"/>
         <v>46311</v>
       </c>
-      <c r="D19" s="4"/>
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="31"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="1"/>
+      <c r="I19" s="1">
+        <v>13</v>
+      </c>
       <c r="J19" s="1">
         <v>20</v>
       </c>
       <c r="K19" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="20" spans="3:11" x14ac:dyDescent="0.3">
@@ -11076,18 +11080,22 @@
         <f t="shared" si="1"/>
         <v>46312</v>
       </c>
-      <c r="D20" s="4"/>
+      <c r="D20" s="4">
+        <v>0</v>
+      </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
+      <c r="G20" s="31"/>
       <c r="H20" s="3"/>
-      <c r="I20" s="1"/>
+      <c r="I20" s="1">
+        <v>11</v>
+      </c>
       <c r="J20" s="1">
         <v>20</v>
       </c>
       <c r="K20" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="21" spans="3:11" x14ac:dyDescent="0.3">
@@ -11095,18 +11103,22 @@
         <f t="shared" si="1"/>
         <v>46313</v>
       </c>
-      <c r="D21" s="4"/>
+      <c r="D21" s="4">
+        <v>1</v>
+      </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
+      <c r="G21" s="32"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="1"/>
+      <c r="I21" s="1">
+        <v>14</v>
+      </c>
       <c r="J21" s="1">
         <v>20</v>
       </c>
       <c r="K21" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="22" spans="3:11" x14ac:dyDescent="0.3">
@@ -11117,7 +11129,7 @@
       <c r="D22" s="4"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
+      <c r="G22" s="31"/>
       <c r="H22" s="3"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1">
@@ -11359,23 +11371,23 @@
     <row r="36" spans="3:11" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.25806451612903225</v>
+        <v>0.32258064516129031</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="1">
         <f>AVERAGE(I4:I34)</f>
-        <v>11.4</v>
+        <v>11.611111111111111</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="5">
         <f>AVERAGE(K4:K34)</f>
-        <v>0.27580645161290318</v>
+        <v>0.33709677419354839</v>
       </c>
     </row>
   </sheetData>
@@ -11421,7 +11433,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -12785,7 +12797,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -13530,7 +13542,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -14463,7 +14475,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -15576,7 +15588,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -16291,7 +16303,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -17021,7 +17033,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -17727,7 +17739,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2683,7 +2683,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -3384,7 +3384,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -4048,7 +4048,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -4773,7 +4773,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -5500,7 +5500,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -6206,7 +6206,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -6939,7 +6939,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -7654,7 +7654,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -8393,7 +8393,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -9144,7 +9144,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -9871,7 +9871,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -10626,7 +10626,7 @@
     <row r="3" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -11126,18 +11126,22 @@
         <f t="shared" si="1"/>
         <v>46314</v>
       </c>
-      <c r="D22" s="4"/>
+      <c r="D22" s="4">
+        <v>1</v>
+      </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="31"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="1"/>
+      <c r="I22" s="1">
+        <v>13</v>
+      </c>
       <c r="J22" s="1">
         <v>20</v>
       </c>
       <c r="K22" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="23" spans="3:11" x14ac:dyDescent="0.3">
@@ -11148,7 +11152,7 @@
       <c r="D23" s="4"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
+      <c r="G23" s="31"/>
       <c r="H23" s="3"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1">
@@ -11371,23 +11375,23 @@
     <row r="36" spans="3:11" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.32258064516129031</v>
+        <v>0.35483870967741937</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="1">
         <f>AVERAGE(I4:I34)</f>
-        <v>11.611111111111111</v>
+        <v>11.684210526315789</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="5">
         <f>AVERAGE(K4:K34)</f>
-        <v>0.33709677419354839</v>
+        <v>0.35806451612903223</v>
       </c>
     </row>
   </sheetData>
@@ -11433,7 +11437,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -12797,7 +12801,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -13542,7 +13546,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -14475,7 +14479,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -15588,7 +15592,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -16303,7 +16307,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -17033,7 +17037,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -17739,7 +17743,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2683,7 +2683,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -3384,7 +3384,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -4048,7 +4048,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -4773,7 +4773,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -5500,7 +5500,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -6206,7 +6206,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -6939,7 +6939,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -7654,7 +7654,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -8393,7 +8393,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -9144,7 +9144,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -9871,7 +9871,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -10626,7 +10626,7 @@
     <row r="3" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -11149,18 +11149,22 @@
         <f t="shared" si="1"/>
         <v>46315</v>
       </c>
-      <c r="D23" s="4"/>
+      <c r="D23" s="4">
+        <v>0</v>
+      </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="31"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="1"/>
+      <c r="I23" s="1">
+        <v>12</v>
+      </c>
       <c r="J23" s="1">
         <v>20</v>
       </c>
       <c r="K23" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="24" spans="3:11" x14ac:dyDescent="0.3">
@@ -11171,7 +11175,7 @@
       <c r="D24" s="4"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
+      <c r="G24" s="32"/>
       <c r="H24" s="3"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1">
@@ -11386,12 +11390,12 @@
       <c r="H36" s="5"/>
       <c r="I36" s="1">
         <f>AVERAGE(I4:I34)</f>
-        <v>11.684210526315789</v>
+        <v>11.7</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="5">
         <f>AVERAGE(K4:K34)</f>
-        <v>0.35806451612903223</v>
+        <v>0.37741935483870964</v>
       </c>
     </row>
   </sheetData>
@@ -11437,7 +11441,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -12801,7 +12805,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -13546,7 +13550,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -14479,7 +14483,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -15592,7 +15596,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -16307,7 +16311,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -17037,7 +17041,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -17743,7 +17747,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2683,7 +2683,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -3384,7 +3384,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -4048,7 +4048,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -4773,7 +4773,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -5500,7 +5500,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -6206,7 +6206,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -6939,7 +6939,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -7654,7 +7654,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -8393,7 +8393,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -9144,7 +9144,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -9871,7 +9871,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -10626,7 +10626,7 @@
     <row r="3" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -11172,18 +11172,22 @@
         <f t="shared" si="1"/>
         <v>46316</v>
       </c>
-      <c r="D24" s="4"/>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="32"/>
       <c r="H24" s="3"/>
-      <c r="I24" s="1"/>
+      <c r="I24" s="1">
+        <v>14</v>
+      </c>
       <c r="J24" s="1">
         <v>20</v>
       </c>
       <c r="K24" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="25" spans="3:11" x14ac:dyDescent="0.3">
@@ -11194,7 +11198,7 @@
       <c r="D25" s="4"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
+      <c r="G25" s="31"/>
       <c r="H25" s="3"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1">
@@ -11379,23 +11383,23 @@
     <row r="36" spans="3:11" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.35483870967741937</v>
+        <v>0.38709677419354838</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="1">
         <f>AVERAGE(I4:I34)</f>
-        <v>11.7</v>
+        <v>11.80952380952381</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="5">
         <f>AVERAGE(K4:K34)</f>
-        <v>0.37741935483870964</v>
+        <v>0.39999999999999997</v>
       </c>
     </row>
   </sheetData>
@@ -11441,7 +11445,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -12805,7 +12809,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -13550,7 +13554,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -14483,7 +14487,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -15596,7 +15600,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -16311,7 +16315,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -17041,7 +17045,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -17747,7 +17751,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2683,7 +2683,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -3384,7 +3384,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -4048,7 +4048,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -4773,7 +4773,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -5500,7 +5500,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -6206,7 +6206,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -6939,7 +6939,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -7654,7 +7654,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -8393,7 +8393,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -9144,7 +9144,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -9871,7 +9871,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -10626,7 +10626,7 @@
     <row r="3" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -11195,18 +11195,22 @@
         <f t="shared" si="1"/>
         <v>46317</v>
       </c>
-      <c r="D25" s="4"/>
+      <c r="D25" s="4">
+        <v>1</v>
+      </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="31"/>
       <c r="H25" s="3"/>
-      <c r="I25" s="1"/>
+      <c r="I25" s="1">
+        <v>14</v>
+      </c>
       <c r="J25" s="1">
         <v>20</v>
       </c>
       <c r="K25" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="26" spans="3:11" x14ac:dyDescent="0.3">
@@ -11217,7 +11221,7 @@
       <c r="D26" s="4"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
+      <c r="G26" s="31"/>
       <c r="H26" s="3"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1">
@@ -11383,23 +11387,23 @@
     <row r="36" spans="3:11" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.38709677419354838</v>
+        <v>0.41935483870967744</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="1">
         <f>AVERAGE(I4:I34)</f>
-        <v>11.80952380952381</v>
+        <v>11.909090909090908</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="5">
         <f>AVERAGE(K4:K34)</f>
-        <v>0.39999999999999997</v>
+        <v>0.42258064516129024</v>
       </c>
     </row>
   </sheetData>
@@ -11445,7 +11449,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -12809,7 +12813,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -13554,7 +13558,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -14487,7 +14491,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -15600,7 +15604,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -16315,7 +16319,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -17045,7 +17049,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -17751,7 +17755,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2683,7 +2683,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -3384,7 +3384,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -4048,7 +4048,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -4773,7 +4773,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -5500,7 +5500,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -6206,7 +6206,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -6939,7 +6939,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -7654,7 +7654,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -8393,7 +8393,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -9144,7 +9144,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -9871,7 +9871,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -10626,7 +10626,7 @@
     <row r="3" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -11218,18 +11218,22 @@
         <f t="shared" si="1"/>
         <v>46318</v>
       </c>
-      <c r="D26" s="4"/>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="31"/>
       <c r="H26" s="3"/>
-      <c r="I26" s="1"/>
+      <c r="I26" s="1">
+        <v>11</v>
+      </c>
       <c r="J26" s="1">
         <v>20</v>
       </c>
       <c r="K26" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="27" spans="3:11" x14ac:dyDescent="0.3">
@@ -11237,18 +11241,22 @@
         <f t="shared" si="1"/>
         <v>46319</v>
       </c>
-      <c r="D27" s="4"/>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
+      <c r="G27" s="31"/>
       <c r="H27" s="3"/>
-      <c r="I27" s="1"/>
+      <c r="I27" s="1">
+        <v>12</v>
+      </c>
       <c r="J27" s="1">
         <v>20</v>
       </c>
       <c r="K27" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="28" spans="3:11" x14ac:dyDescent="0.3">
@@ -11256,18 +11264,22 @@
         <f t="shared" si="1"/>
         <v>46320</v>
       </c>
-      <c r="D28" s="4"/>
+      <c r="D28" s="4">
+        <v>1</v>
+      </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
+      <c r="G28" s="32"/>
       <c r="H28" s="3"/>
-      <c r="I28" s="1"/>
+      <c r="I28" s="1">
+        <v>12</v>
+      </c>
       <c r="J28" s="1">
         <v>20</v>
       </c>
       <c r="K28" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="29" spans="3:11" x14ac:dyDescent="0.3">
@@ -11275,18 +11287,22 @@
         <f t="shared" si="1"/>
         <v>46321</v>
       </c>
-      <c r="D29" s="4"/>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
+      <c r="G29" s="32"/>
       <c r="H29" s="3"/>
-      <c r="I29" s="1"/>
+      <c r="I29" s="1">
+        <v>14</v>
+      </c>
       <c r="J29" s="1">
         <v>20</v>
       </c>
       <c r="K29" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="30" spans="3:11" x14ac:dyDescent="0.3">
@@ -11297,7 +11313,7 @@
       <c r="D30" s="4"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
+      <c r="G30" s="32"/>
       <c r="H30" s="3"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1">
@@ -11387,23 +11403,23 @@
     <row r="36" spans="3:11" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.41935483870967744</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="1">
         <f>AVERAGE(I4:I34)</f>
-        <v>11.909090909090908</v>
+        <v>11.961538461538462</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="5">
         <f>AVERAGE(K4:K34)</f>
-        <v>0.42258064516129024</v>
+        <v>0.50161290322580632</v>
       </c>
     </row>
   </sheetData>
@@ -11449,7 +11465,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -12813,7 +12829,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -13558,7 +13574,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -14491,7 +14507,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -15604,7 +15620,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -16319,7 +16335,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -17049,7 +17065,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -17755,7 +17771,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2683,7 +2683,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -3384,7 +3384,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -4048,7 +4048,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -4773,7 +4773,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -5500,7 +5500,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -6206,7 +6206,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -6939,7 +6939,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -7654,7 +7654,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -8393,7 +8393,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -9144,7 +9144,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -9871,7 +9871,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -10626,7 +10626,7 @@
     <row r="3" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -11310,18 +11310,22 @@
         <f t="shared" si="1"/>
         <v>46322</v>
       </c>
-      <c r="D30" s="4"/>
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="32"/>
       <c r="H30" s="3"/>
-      <c r="I30" s="1"/>
+      <c r="I30" s="1">
+        <v>15</v>
+      </c>
       <c r="J30" s="1">
         <v>20</v>
       </c>
       <c r="K30" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="31" spans="3:11" x14ac:dyDescent="0.3">
@@ -11332,7 +11336,7 @@
       <c r="D31" s="4"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
+      <c r="G31" s="31"/>
       <c r="H31" s="3"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1">
@@ -11403,23 +11407,23 @@
     <row r="36" spans="3:11" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.4838709677419355</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="1">
         <f>AVERAGE(I4:I34)</f>
-        <v>11.961538461538462</v>
+        <v>12.074074074074074</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="5">
         <f>AVERAGE(K4:K34)</f>
-        <v>0.50161290322580632</v>
+        <v>0.52580645161290318</v>
       </c>
     </row>
   </sheetData>
@@ -11465,7 +11469,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -12829,7 +12833,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -13574,7 +13578,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -14507,7 +14511,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -15620,7 +15624,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -16335,7 +16339,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -17065,7 +17069,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -17771,7 +17775,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2683,7 +2683,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -3384,7 +3384,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -4048,7 +4048,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -4773,7 +4773,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -5500,7 +5500,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -6206,7 +6206,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -6939,7 +6939,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -7654,7 +7654,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -8393,7 +8393,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -9144,7 +9144,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -9871,7 +9871,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -10626,7 +10626,7 @@
     <row r="3" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -11006,7 +11006,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C17" s="3">
         <f t="shared" si="1"/>
         <v>46309</v>
@@ -11029,7 +11029,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C18" s="3">
         <f t="shared" si="1"/>
         <v>46310</v>
@@ -11052,7 +11052,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C19" s="3">
         <f t="shared" si="1"/>
         <v>46311</v>
@@ -11075,7 +11075,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C20" s="3">
         <f t="shared" si="1"/>
         <v>46312</v>
@@ -11098,7 +11098,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C21" s="3">
         <f t="shared" si="1"/>
         <v>46313</v>
@@ -11121,7 +11121,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C22" s="3">
         <f t="shared" si="1"/>
         <v>46314</v>
@@ -11144,7 +11144,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C23" s="3">
         <f t="shared" si="1"/>
         <v>46315</v>
@@ -11167,7 +11167,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C24" s="3">
         <f t="shared" si="1"/>
         <v>46316</v>
@@ -11190,7 +11190,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C25" s="3">
         <f t="shared" si="1"/>
         <v>46317</v>
@@ -11213,7 +11213,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C26" s="3">
         <f t="shared" si="1"/>
         <v>46318</v>
@@ -11236,7 +11236,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C27" s="3">
         <f t="shared" si="1"/>
         <v>46319</v>
@@ -11259,7 +11259,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C28" s="3">
         <f t="shared" si="1"/>
         <v>46320</v>
@@ -11282,7 +11282,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C29" s="3">
         <f t="shared" si="1"/>
         <v>46321</v>
@@ -11305,7 +11305,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C30" s="3">
         <f t="shared" si="1"/>
         <v>46322</v>
@@ -11328,26 +11328,63 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C31" s="3">
         <f t="shared" si="1"/>
         <v>46323</v>
       </c>
-      <c r="D31" s="4"/>
+      <c r="D31" s="4">
+        <v>1</v>
+      </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="31"/>
       <c r="H31" s="3"/>
-      <c r="I31" s="1"/>
+      <c r="I31" s="1">
+        <v>14</v>
+      </c>
       <c r="J31" s="1">
         <v>20</v>
       </c>
       <c r="K31" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.3">
+        <v>0.7</v>
+      </c>
+      <c r="M31">
+        <v>154</v>
+      </c>
+      <c r="N31">
+        <v>169</v>
+      </c>
+      <c r="O31">
+        <v>170</v>
+      </c>
+      <c r="P31">
+        <v>177</v>
+      </c>
+      <c r="Q31">
+        <v>178</v>
+      </c>
+      <c r="R31">
+        <v>184</v>
+      </c>
+      <c r="S31">
+        <v>186</v>
+      </c>
+      <c r="U31">
+        <v>163</v>
+      </c>
+      <c r="V31">
+        <v>157</v>
+      </c>
+      <c r="W31">
+        <v>150</v>
+      </c>
+      <c r="X31" s="25">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C32" s="3">
         <f t="shared" si="1"/>
         <v>46324</v>
@@ -11355,7 +11392,7 @@
       <c r="D32" s="4"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
+      <c r="G32" s="31"/>
       <c r="H32" s="3"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1">
@@ -11407,23 +11444,23 @@
     <row r="36" spans="3:11" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.5161290322580645</v>
+        <v>0.54838709677419351</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="1">
         <f>AVERAGE(I4:I34)</f>
-        <v>12.074074074074074</v>
+        <v>12.142857142857142</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="5">
         <f>AVERAGE(K4:K34)</f>
-        <v>0.52580645161290318</v>
+        <v>0.54838709677419339</v>
       </c>
     </row>
   </sheetData>
@@ -11469,7 +11506,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -12833,7 +12870,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -13578,7 +13615,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -14511,7 +14548,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -15624,7 +15661,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -16339,7 +16376,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -17069,7 +17106,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -17775,7 +17812,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="33360" yWindow="5715" windowWidth="28800" windowHeight="15885" activeTab="1"/>
+    <workbookView xWindow="33360" yWindow="5715" windowWidth="28800" windowHeight="15885" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="_Base" sheetId="2" r:id="rId1"/>
@@ -2683,7 +2683,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -3384,7 +3384,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -4048,7 +4048,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -4773,7 +4773,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -5500,7 +5500,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -6206,7 +6206,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -6939,7 +6939,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -7654,7 +7654,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -8393,7 +8393,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -9144,7 +9144,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -9871,7 +9871,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -10626,7 +10626,7 @@
     <row r="3" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -11389,18 +11389,22 @@
         <f t="shared" si="1"/>
         <v>46324</v>
       </c>
-      <c r="D32" s="4"/>
+      <c r="D32" s="4">
+        <v>1</v>
+      </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="31"/>
       <c r="H32" s="3"/>
-      <c r="I32" s="1"/>
+      <c r="I32" s="1">
+        <v>13</v>
+      </c>
       <c r="J32" s="1">
         <v>20</v>
       </c>
       <c r="K32" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="33" spans="3:11" x14ac:dyDescent="0.3">
@@ -11411,7 +11415,7 @@
       <c r="D33" s="4"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
+      <c r="G33" s="31"/>
       <c r="H33" s="3"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1">
@@ -11444,23 +11448,23 @@
     <row r="36" spans="3:11" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.54838709677419351</v>
+        <v>0.58064516129032262</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="1">
         <f>AVERAGE(I4:I34)</f>
-        <v>12.142857142857142</v>
+        <v>12.172413793103448</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="5">
         <f>AVERAGE(K4:K34)</f>
-        <v>0.54838709677419339</v>
+        <v>0.56935483870967729</v>
       </c>
     </row>
   </sheetData>
@@ -11506,7 +11510,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -12870,7 +12874,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -13615,7 +13619,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -14548,7 +14552,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -15661,7 +15665,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -16376,7 +16380,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -17106,7 +17110,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
@@ -17812,7 +17816,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="35" t="s">
